--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry Logs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry Logs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,1697 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1-s2.0-S1665268124005349-main.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The burden of hepatic encephalopathy and the use of albumin as a potential treatment</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jasmohan S. Bajaj, Enrico Pompili, Paolo Caraceni</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Annals of Hepatology</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10.1016/j.aohep.2024.101751</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gastroenterology/Hepatology</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:27:03</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2110582025020321-main.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Remote ischemic conditioning in intensive care: From bench to bedside</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sarah Benghanem et al.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Annals of Intensive Care</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.1016/j.aicoj.2025.100018</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Critical Care / Multi-system</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:27:54</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2110582026000658-main.pdf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bedside ventilatory settings guided by respiratory mechanics in acute respiratory distress syndrome</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Davide Chiumello et al.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Annals of Intensive Care</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s13613-025-01606-0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pulmonology / Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:28:48</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chronic-hepatitis-B-in-2025--diagnosis--treatment-and-fut_2025_Clinical-Medi.pdf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B in 2025: diagnosis, treatment and future directions</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Andrew G. Watson et al.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10.1016/j.clinme.2025.100527</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:29:15</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>e001369.full.pdf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Intraosseous access in the resuscitation of patients with trauma: the good, the bad, the future</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Zaffer A Qasim et al.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Trauma Surgery &amp; Acute Care Open</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10.1136/tsaco-2024-001369</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Trauma / Emergency Medicine / Vascular Access</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:30:24</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>evidence_based,_cost_effective_management_of_lower.1388.pdf</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Evidence-based, cost-effective management of lower gastrointestinal bleeding. An algorithm of the journal of trauma and acute care surgery emergency general surgery algorithms work group</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>David H. Livingston et al.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Journal of Trauma and Acute Care Surgery</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10.1097/TA.0000000000005074</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gastroenterology / Emergency General Surgery</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:30:57</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fmed-13-1775538.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The neurological phoenix: multimodal strategies for brain recovery and prognostication in post-cardiac arrest syndrome—a 2025 clinical framework</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Said Kortli and Prashant Nasa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Frontiers in Medicine</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10.3389/fmed.2026.1775538</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neurology / Intensive Care</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:31:54</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gut_microbiome_brain_cirrhosis_axis.19.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gut microbiome-brain-cirrhosis axis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Maren L. Smith et al.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10.1097/HEP.0000000000000344</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatology / Neuro-Gastroenterology</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:32:54</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hepatitis-C--current-treatments--emerging-therapies-and-tackli_2025_Clinical.pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hepatitis C: current treatments, emerging therapies and tackling health inequities on the path to global elimination</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hamzah Z. Farooq et al.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.clinme.2025.100522</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:33:24</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hepatocellular-carcinoma--HCC---An-update-on-risk-factors--su_2025_Clinical-.pdf</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hepatocellular carcinoma (HCC): An update on risk factors, surveillance, diagnosis and treatment strategies</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sanju Mathew et al.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10.1016/j.clinme.2025.100532</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:34:06</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>jcm-14-02067.pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Acute Respiratory Distress Syndrome and Fluid Management: Finding the Perfect Balance</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sbaraini Zernini et al.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Journal of Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10.3390/jcm14062067</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pulmonology / Critical Care</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:34:57</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ketamine for status epilepticus.pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ketamine in Status Epilepticus: How Soon Is Now?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Giuseppe Magro</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Neurology International</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/neurolint17060083</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neurology / Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:36:03</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Management-of-acute-decompensated-cirrhosis_2025_Clinical-Medicine.pdf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Management of acute decompensated cirrhosis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Dina Mansour</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.clinme.2025.100534</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatology / Gastroenterology</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:36:30</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Metabolic-dysfunction-associated-steatotic-liver-disea_2025_Clinical-Medicin.pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Metabolic dysfunction-associated steatotic liver disease</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Catherine Hsu et al.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10.1016/j.clinme.2025.100526</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:36:52</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nutrients-18-01359.pdf</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Magnesium in Neurocritical Care: Clinical Relevance, Status Assessment, and Practical Implications for Outcomes—A Narrative Review</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stefano Marelli et al.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nutrients</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/nu18091359</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neurology / Neurocritical Care</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:37:40</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nutrition in ICU.pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nutrition support in the ICU: current evidence and evolving standards</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>S. L. Peake et al.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Intensive Care Medicine</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00134-026-08474-7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Critical Care / Clinical Nutrition</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:38:35</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Palliative-care-in-advanced-liver-disease_2025_Clinical-Medicine.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Palliative care in advanced liver disease</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Christopher Cussen et al.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.clinme.2025.100529</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatology / Palliative Care</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:38:54</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pathophysiology-33-00036.pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>From Glycocalyx Shedding to Microvascular Collapse in Sepsis: Endothelial Pathophysiology, Organ Dysfunction, and Mechanistic Biomarkers</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jhan S. Saavedra-Torres et al.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pathophysiology</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/pathophysiology33020036</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Critical Care / Cardiovascular / Pulmonology</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:39:49</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PIIS2772930324000681.pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The Intra-aortic Balloon Pump: A Focused Review of Physiology, Transport Logistics, Mechanics, and Complications</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lauren E. Gillespie, MD et al.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Journal of the Society for Cardiovascular Angiography &amp; Interventions</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10.1016/j.jscai.2024.101337</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:40:53</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prophylaxis_of_venous_thromboembolism_in_trauma_.2.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Prophylaxis of venous thromboembolism in trauma: What you need to know</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Michelle Lippincott et al.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Journal of Trauma and Acute Care Surgery</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10.1097/TA.0000000000004871</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Trauma Surgery / Surgical Critical Care / Hematology</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:41:45</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>s00134-026-08496-1.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Acute respiratory distress mimickers: a practical approach for intensivists</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pierre Bay et al.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Intensive Care Medicine</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00134-026-08496-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pulmonology / Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:42:04</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>s00134-026-08503-5.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Imaging in ARDS: physiology-guided decisions in the AI era</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lorenzo Ball et al.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Intensive Care Medicine</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00134-026-08503-5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pulmonology / Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:42:20</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>s12028-023-01752-y.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Practice Guidance for the Critical Care Management of SAH: Intracranial Pressure Monitoring and Management in Aneurysmal Subarachnoid Hemorrhage</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Alberto Addis, Marta Baggiani, and Giuseppe Citerio</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Neurocritical Care</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10.1007/s12028-023-01752-y</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Neurology / Neurocritical Care</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Guideline/Review</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:42:29</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>s12245-025-01078-w.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A narrative review of the diabetic ketoacidosis and hyperosmolar hyperglycemic state overlap syndrome</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Eslam Abady, Panos I. Tamvakologos, Marina Ramzy Mourid, et al.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>International Journal of Emergency Medicine</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10.1186/s12245-025-01078-w</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Endocrinology / Emergency Medicine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:42:37</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>s15010-026-02852-5.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The evolution of sepsis care: from protocol-driven management to personalized intensive care</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tim Rahmel et al.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10.1007/s15010-026-02852-5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:42:50</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>surviving_sepsis_campaign__international.5.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Extraction Error: surviving_sepsis_campaign__international.5.pdf</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-21 15:43:17</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Failed during processing pass: All processing model layers exhausted. Execution halted. Last exception: Expecting ',' delimiter: li</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry Logs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry Logs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -673,7 +673,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -681,6 +681,11 @@
           <t>2026-06-21 15:27:03</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-06-21 10:24:54</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Success</t>
@@ -688,7 +693,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2311,6 @@
           <t>2026-06-21 15:43:17</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Failed during processing pass: All processing model layers exhausted. Execution halted. Last exception: Expecting ',' delimiter: li</t>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry Logs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry Logs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -751,6 +751,11 @@
           <t>2026-06-21 15:27:54</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:26:31</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Success</t>
@@ -758,7 +763,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="39.77734375" customWidth="1" min="6" max="6"/>
@@ -2340,6 +2340,1177 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Acute-confusion-in-pregnancy_2025_Clinical-Medicine.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Acute confusion in pregnancy</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Amanda Hill et al.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.clinme.2024.100273</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynecology / Acute Medicine / Neurology</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:04:47</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Approach-to-investigation-and-management-of-proteinuria-i_2025_Clinical-Medi.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Approach to investigation and management of proteinuria in pregnancy</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Isabela Bertoni, Sion Williams</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10.1016/j.clinme.2024.100281</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephrology / Obstetric Medicine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:05:35</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Management-of-asthma-in-pregnancy_2025_Clinical-Medicine.pdf</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Management of asthma in pregnancy</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C.E. Jones et al.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10.1016/j.clinme.2024.100277</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pulmonology / Obstetrics</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Guideline / Clinical Review</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:05:57</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Severe-acute-pulmonary-embolism-in-pregnancy_2025_Clinical-Medicine.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Severe acute pulmonary embolism in pregnancy</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bhaskar Narayan</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10.1016/j.clinme.2024.100274</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CVS / Pulmonology / Obstetrics</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:06:50</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>acc-000884.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Managing sepsis in the era of precision medicine: a narrative review</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ho Jin Yong et al.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Acute and Critical Care</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4266/acc.000884</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Critical Care / Pulmonology / Infectious Diseases</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:28:34</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>acc-003425.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Beyond blood pressure: a comprehensive overview of clinical indices in shock and tissue hypoperfusion</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jooyun Kim et al.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Acute and Critical Care</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4266/acc.003425</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cardiovascular System / Critical Care</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:30:36</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>current_management_of_traumatic_intracranial.1.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Current management of traumatic intracranial hypertension: What you need to know</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Alex B. Valadka et al.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Journal of Trauma and Acute Care Surgery</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10.1097/TA.0000000000004921</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neurology/Neurosurgery</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:33:25</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>s10877-026-01457-5.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Echocardiography before non-cardiac surgery: current knowledge, guideline recommendations, and clinical evidence – a narrative review</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Viktoria Mertin, Alexandra Stroda, Tobias Bruns, Giovanna Lurati Buse</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Journal of Clinical Monitoring and Computing</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10.1007/s10877-026-01457-5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CVS / Anesthesiology</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:33:35</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>s12028-026-02565-5.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Safety and Additive Efficacy of Dual CSF Drainage (Ventricular + Lumbar) in Severe Aneurysmal Subarachnoid Hemorrhage: A Secondary Analysis of the EARLYDRAIN Trial</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Gianluca Trevisi, Matteo Palermo, et al.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Neurocrit Care</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10.1007/s12028-026-02565-5</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neurosurgery / Neurocritical Care</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Secondary Analysis of a Clinical Trial</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:35:33</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>s13054-026-06142-2_reference.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Comparative efficacy and safety of extended versus continuous infusion of beta-lactam antibiotics for severe infection: a network meta-analysis of randomized trials</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Zhou L. et al.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Critical Care</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s13054-026-06142-2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Infectious Diseases / Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Network Meta-Analysis of Randomized Trials</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:36:34</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>s13054-026-06144-0.pdf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Implementation of the kidney protection strategy in critically ill patients with acute kidney injury – a multi-center prospective cohort study</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Mahan Sadjadi et al.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Critical Care</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s13054-026-06144-0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephrology / Critical Care</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Observational</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:37:21</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2667100X26001180-main.pdf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>The potential role of methylene blue as an adjunctive therapy in septic shock</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Xinxin Cui, Jian Song, et al.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Journal of Intensive Medicine</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10.1016/j.jointm.2026.05.002</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Perspective</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:03:19</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>jcm-15-04453.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mechanical Support in Myocardial Infarction Complicated by Cardiogenic Shock: What Have We Learned from Trials?</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Cristina Aurigemma et al.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Journal of Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/jcm15124453</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cardiovascular System / Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:31:53</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>s13054-026-06111-9.pdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>The effects of mechanical ventilation during v-a ecmo support: a systematic review</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ilaria Protti et al.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Critical Care</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1186/s13054-026-06111-9</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CVS / Pulmonology</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:32:23</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>diagnostic_and_prognostic_value_of_the_venous.875.pdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Diagnostic and Prognostic Value of the Venous Excess Ultrasound Grading System: A Systematic Review and Meta-Analysis</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Peter Klompmaker et al.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10.1097/CCM.0000000000007219</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cardiovascular System (CVS) / Nephrology / Critical Care Ultrasound</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-06-23 08:32:56</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>magnesium_sulfate_to_prevent_perioperative_atrial.847.pdf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Magnesium Sulfate to Prevent Perioperative Atrial Fibrillation in Cardiac Surgery: A Randomized Clinical Trial</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Manon Meerman, MD et al.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10.1097/CCM.0000000000007162</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cardiovascular System / Cardiothoracic Surgery</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:00:57</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PIIS103673142600041X.pdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Heparinised saline versus normal saline flushing in maintaining arterial catheter patency in intensive care patients: A systematic review and meta-analysis of randomised controlled trials</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Guglielmo Imbriaco, RN, MSN, Lorenzo Gamberini, MD, et al.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Australian Critical Care</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10.1016/j.aucc.2026.101571</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Critical Care / Vascular Access</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:01:47</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>s00134-026-08459-6.pdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Personalized automatic management of tracheal cuff pressure and subglottic secretions drainage to prevent pneumonia in critically ill intubated patients. The MICROINHALO multicenter randomized controlled trial</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>De Pascale et al.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Intensive Care Medicine</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00134-026-08459-6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pulmonology / Critical Care Medicine / Infectious Diseases</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:02:23</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -45,8 +45,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,10 +415,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="39.77734375" customWidth="1" min="6" max="6"/>
+    <col width="39.88671875" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50.44140625" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -429,7 +434,7 @@
           <t>File Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Paper/Guideline Name</t>
         </is>
@@ -490,7 +495,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28.8" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -499,7 +504,7 @@
           <t>advances_in_achieving_lung_and.7.pdf</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Advances in achieving lung and diaphragm-protective ventilation</t>
         </is>
@@ -521,7 +526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulmonology / Critical Care Medicine</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,7 +574,7 @@
           <t>s13054-023-04632-1.pdf</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Acute kidney injury in neurocritical care</t>
         </is>
@@ -591,7 +596,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephrology / Neurology</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,7 +635,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28.8" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -639,7 +644,7 @@
           <t>1-s2.0-S1665268124005349-main.pdf</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>The burden of hepatic encephalopathy and the use of albumin as a potential treatment</t>
         </is>
@@ -661,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gastroenterology/Hepatology</t>
+          <t>Hepatology</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -700,7 +705,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="28.8" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -709,7 +714,7 @@
           <t>1-s2.0-S2110582025020321-main.pdf</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Remote ischemic conditioning in intensive care: From bench to bedside</t>
         </is>
@@ -731,7 +736,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Critical Care / Multi-system</t>
+          <t>Multi-system</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -770,7 +775,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="43.2" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -779,7 +784,7 @@
           <t>1-s2.0-S2110582026000658-main.pdf</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>Bedside ventilatory settings guided by respiratory mechanics in acute respiratory distress syndrome</t>
         </is>
@@ -801,7 +806,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulmonology / Critical Care Medicine</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -835,7 +840,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="28.8" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -844,7 +849,7 @@
           <t>Chronic-hepatitis-B-in-2025--diagnosis--treatment-and-fut_2025_Clinical-Medi.pdf</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Chronic hepatitis B in 2025: diagnosis, treatment and future directions</t>
         </is>
@@ -900,7 +905,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="43.2" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -909,7 +914,7 @@
           <t>e001369.full.pdf</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>Intraosseous access in the resuscitation of patients with trauma: the good, the bad, the future</t>
         </is>
@@ -931,7 +936,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trauma / Emergency Medicine / Vascular Access</t>
+          <t>Trauma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -965,7 +970,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -974,7 +979,7 @@
           <t>evidence_based,_cost_effective_management_of_lower.1388.pdf</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>Evidence-based, cost-effective management of lower gastrointestinal bleeding. An algorithm of the journal of trauma and acute care surgery emergency general surgery algorithms work group</t>
         </is>
@@ -996,7 +1001,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gastroenterology / Emergency General Surgery</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1030,7 +1035,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="57.6" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -1039,7 +1044,7 @@
           <t>fmed-13-1775538.pdf</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>The neurological phoenix: multimodal strategies for brain recovery and prognostication in post-cardiac arrest syndrome—a 2025 clinical framework</t>
         </is>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neurology / Intensive Care</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1104,7 +1109,7 @@
           <t>gut_microbiome_brain_cirrhosis_axis.19.pdf</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Gut microbiome-brain-cirrhosis axis</t>
         </is>
@@ -1126,7 +1131,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatology / Neuro-Gastroenterology</t>
+          <t>Hepatology</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1160,7 +1165,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="43.2" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -1169,7 +1174,7 @@
           <t>Hepatitis-C--current-treatments--emerging-therapies-and-tackli_2025_Clinical.pdf</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>Hepatitis C: current treatments, emerging therapies and tackling health inequities on the path to global elimination</t>
         </is>
@@ -1225,7 +1230,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="43.2" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -1234,7 +1239,7 @@
           <t>Hepatocellular-carcinoma--HCC---An-update-on-risk-factors--su_2025_Clinical-.pdf</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>Hepatocellular carcinoma (HCC): An update on risk factors, surveillance, diagnosis and treatment strategies</t>
         </is>
@@ -1290,7 +1295,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="28.8" customHeight="1">
       <c r="A14" t="n">
         <v>13</v>
       </c>
@@ -1299,7 +1304,7 @@
           <t>jcm-14-02067.pdf</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>Acute Respiratory Distress Syndrome and Fluid Management: Finding the Perfect Balance</t>
         </is>
@@ -1321,7 +1326,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pulmonology / Critical Care</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1360,7 +1365,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="28.8" customHeight="1">
       <c r="A15" t="n">
         <v>14</v>
       </c>
@@ -1369,7 +1374,7 @@
           <t>Ketamine for status epilepticus.pdf</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Ketamine in Status Epilepticus: How Soon Is Now?</t>
         </is>
@@ -1391,7 +1396,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neurology / Critical Care Medicine</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1425,7 +1430,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="28.8" customHeight="1">
       <c r="A16" t="n">
         <v>15</v>
       </c>
@@ -1434,7 +1439,7 @@
           <t>Management-of-acute-decompensated-cirrhosis_2025_Clinical-Medicine.pdf</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Management of acute decompensated cirrhosis</t>
         </is>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatology / Gastroenterology</t>
+          <t>Hepatology</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1490,7 +1495,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="28.8" customHeight="1">
       <c r="A17" t="n">
         <v>16</v>
       </c>
@@ -1499,7 +1504,7 @@
           <t>Metabolic-dysfunction-associated-steatotic-liver-disea_2025_Clinical-Medicin.pdf</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>Metabolic dysfunction-associated steatotic liver disease</t>
         </is>
@@ -1555,7 +1560,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="57.6" customHeight="1">
       <c r="A18" t="n">
         <v>17</v>
       </c>
@@ -1564,7 +1569,7 @@
           <t>nutrients-18-01359.pdf</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>Magnesium in Neurocritical Care: Clinical Relevance, Status Assessment, and Practical Implications for Outcomes—A Narrative Review</t>
         </is>
@@ -1586,7 +1591,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neurology / Neurocritical Care</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1620,7 +1625,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="28.8" customHeight="1">
       <c r="A19" t="n">
         <v>18</v>
       </c>
@@ -1629,7 +1634,7 @@
           <t>Nutrition in ICU.pdf</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>Nutrition support in the ICU: current evidence and evolving standards</t>
         </is>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Critical Care / Clinical Nutrition</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1694,7 +1699,7 @@
           <t>Palliative-care-in-advanced-liver-disease_2025_Clinical-Medicine.pdf</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>Palliative care in advanced liver disease</t>
         </is>
@@ -1716,7 +1721,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatology / Palliative Care</t>
+          <t>Hepatology</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1750,7 +1755,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="57.6" customHeight="1">
       <c r="A21" t="n">
         <v>20</v>
       </c>
@@ -1759,7 +1764,7 @@
           <t>pathophysiology-33-00036.pdf</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>From Glycocalyx Shedding to Microvascular Collapse in Sepsis: Endothelial Pathophysiology, Organ Dysfunction, and Mechanistic Biomarkers</t>
         </is>
@@ -1781,7 +1786,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Critical Care / Cardiovascular / Pulmonology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1815,7 +1820,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="43.2" customHeight="1">
       <c r="A22" t="n">
         <v>21</v>
       </c>
@@ -1824,7 +1829,7 @@
           <t>PIIS2772930324000681.pdf</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>The Intra-aortic Balloon Pump: A Focused Review of Physiology, Transport Logistics, Mechanics, and Complications</t>
         </is>
@@ -1846,7 +1851,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1880,7 +1885,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="28.8" customHeight="1">
       <c r="A23" t="n">
         <v>22</v>
       </c>
@@ -1889,7 +1894,7 @@
           <t>prophylaxis_of_venous_thromboembolism_in_trauma_.2.pdf</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Prophylaxis of venous thromboembolism in trauma: What you need to know</t>
         </is>
@@ -1911,7 +1916,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trauma Surgery / Surgical Critical Care / Hematology</t>
+          <t>Trauma Surgery</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1950,7 +1955,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="28.8" customHeight="1">
       <c r="A24" t="n">
         <v>23</v>
       </c>
@@ -1959,7 +1964,7 @@
           <t>s00134-026-08496-1.pdf</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>Acute respiratory distress mimickers: a practical approach for intensivists</t>
         </is>
@@ -1981,7 +1986,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pulmonology / Critical Care Medicine</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2015,7 +2020,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="28.8" customHeight="1">
       <c r="A25" t="n">
         <v>24</v>
       </c>
@@ -2024,7 +2029,7 @@
           <t>s00134-026-08503-5.pdf</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Imaging in ARDS: physiology-guided decisions in the AI era</t>
         </is>
@@ -2046,7 +2051,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pulmonology / Critical Care Medicine</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2080,7 +2085,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="57.6" customHeight="1">
       <c r="A26" t="n">
         <v>25</v>
       </c>
@@ -2089,7 +2094,7 @@
           <t>s12028-023-01752-y.pdf</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Practice Guidance for the Critical Care Management of SAH: Intracranial Pressure Monitoring and Management in Aneurysmal Subarachnoid Hemorrhage</t>
         </is>
@@ -2111,7 +2116,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neurology / Neurocritical Care</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2145,7 +2150,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="43.2" customHeight="1">
       <c r="A27" t="n">
         <v>26</v>
       </c>
@@ -2154,7 +2159,7 @@
           <t>s12245-025-01078-w.pdf</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>A narrative review of the diabetic ketoacidosis and hyperosmolar hyperglycemic state overlap syndrome</t>
         </is>
@@ -2176,7 +2181,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Endocrinology / Emergency Medicine</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2210,7 +2215,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="43.2" customHeight="1">
       <c r="A28" t="n">
         <v>27</v>
       </c>
@@ -2219,7 +2224,7 @@
           <t>s15010-026-02852-5.pdf</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>The evolution of sepsis care: from protocol-driven management to personalized intensive care</t>
         </is>
@@ -2241,7 +2246,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Critical Care Medicine</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2275,71 +2280,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>surviving_sepsis_campaign__international.5.pdf</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Extraction Error: surviving_sepsis_campaign__international.5.pdf</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Unknown Authors</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unknown Journal</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2026-06-21 15:43:17</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Failed during processing pass: All processing model layers exhausted. Execution halted. Last exception: Expecting ',' delimiter: li</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
@@ -2349,7 +2290,7 @@
           <t>Acute-confusion-in-pregnancy_2025_Clinical-Medicine.pdf</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Acute confusion in pregnancy</t>
         </is>
@@ -2371,7 +2312,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynecology / Acute Medicine / Neurology</t>
+          <t>Obstetrics and Gynecology</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2405,7 +2346,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="28.8" customHeight="1">
       <c r="A31" t="n">
         <v>30</v>
       </c>
@@ -2414,7 +2355,7 @@
           <t>Approach-to-investigation-and-management-of-proteinuria-i_2025_Clinical-Medi.pdf</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>Approach to investigation and management of proteinuria in pregnancy</t>
         </is>
@@ -2436,7 +2377,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephrology / Obstetric Medicine</t>
+          <t>Obstetrics and Gynecology</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2479,7 +2420,7 @@
           <t>Management-of-asthma-in-pregnancy_2025_Clinical-Medicine.pdf</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>Management of asthma in pregnancy</t>
         </is>
@@ -2501,7 +2442,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pulmonology / Obstetrics</t>
+          <t>Obstetrics and Gynecology</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2535,7 +2476,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="28.8" customHeight="1">
       <c r="A33" t="n">
         <v>32</v>
       </c>
@@ -2544,7 +2485,7 @@
           <t>Severe-acute-pulmonary-embolism-in-pregnancy_2025_Clinical-Medicine.pdf</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>Severe acute pulmonary embolism in pregnancy</t>
         </is>
@@ -2566,7 +2507,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CVS / Pulmonology / Obstetrics</t>
+          <t>Obstetrics and Gynecology</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2600,7 +2541,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="28.8" customHeight="1">
       <c r="A34" t="n">
         <v>33</v>
       </c>
@@ -2609,7 +2550,7 @@
           <t>acc-000884.pdf</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>Managing sepsis in the era of precision medicine: a narrative review</t>
         </is>
@@ -2631,7 +2572,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Critical Care / Pulmonology / Infectious Diseases</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2665,7 +2606,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="43.2" customHeight="1">
       <c r="A35" t="n">
         <v>34</v>
       </c>
@@ -2674,7 +2615,7 @@
           <t>acc-003425.pdf</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>Beyond blood pressure: a comprehensive overview of clinical indices in shock and tissue hypoperfusion</t>
         </is>
@@ -2696,7 +2637,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cardiovascular System / Critical Care</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2730,7 +2671,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="28.8" customHeight="1">
       <c r="A36" t="n">
         <v>35</v>
       </c>
@@ -2739,7 +2680,7 @@
           <t>current_management_of_traumatic_intracranial.1.pdf</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>Current management of traumatic intracranial hypertension: What you need to know</t>
         </is>
@@ -2761,7 +2702,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neurology/Neurosurgery</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2795,7 +2736,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="57.6" customHeight="1">
       <c r="A37" t="n">
         <v>36</v>
       </c>
@@ -2804,7 +2745,7 @@
           <t>s10877-026-01457-5.pdf</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>Echocardiography before non-cardiac surgery: current knowledge, guideline recommendations, and clinical evidence – a narrative review</t>
         </is>
@@ -2826,7 +2767,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CVS / Anesthesiology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2860,7 +2801,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="57.6" customHeight="1">
       <c r="A38" t="n">
         <v>37</v>
       </c>
@@ -2869,7 +2810,7 @@
           <t>s12028-026-02565-5.pdf</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>Safety and Additive Efficacy of Dual CSF Drainage (Ventricular + Lumbar) in Severe Aneurysmal Subarachnoid Hemorrhage: A Secondary Analysis of the EARLYDRAIN Trial</t>
         </is>
@@ -2891,7 +2832,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neurosurgery / Neurocritical Care</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2925,7 +2866,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="57.6" customHeight="1">
       <c r="A39" t="n">
         <v>38</v>
       </c>
@@ -2934,7 +2875,7 @@
           <t>s13054-026-06142-2_reference.pdf</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>Comparative efficacy and safety of extended versus continuous infusion of beta-lactam antibiotics for severe infection: a network meta-analysis of randomized trials</t>
         </is>
@@ -2956,7 +2897,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Infectious Diseases / Critical Care Medicine</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2990,7 +2931,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="57.6" customHeight="1">
       <c r="A40" t="n">
         <v>39</v>
       </c>
@@ -2999,7 +2940,7 @@
           <t>s13054-026-06144-0.pdf</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>Implementation of the kidney protection strategy in critically ill patients with acute kidney injury – a multi-center prospective cohort study</t>
         </is>
@@ -3021,7 +2962,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephrology / Critical Care</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3055,7 +2996,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="28.8" customHeight="1">
       <c r="A41" t="n">
         <v>40</v>
       </c>
@@ -3064,7 +3005,7 @@
           <t>1-s2.0-S2667100X26001180-main.pdf</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>The potential role of methylene blue as an adjunctive therapy in septic shock</t>
         </is>
@@ -3086,7 +3027,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Critical Care Medicine</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3120,7 +3061,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="43.2" customHeight="1">
       <c r="A42" t="n">
         <v>41</v>
       </c>
@@ -3129,7 +3070,7 @@
           <t>jcm-15-04453.pdf</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>Mechanical Support in Myocardial Infarction Complicated by Cardiogenic Shock: What Have We Learned from Trials?</t>
         </is>
@@ -3151,7 +3092,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cardiovascular System / Critical Care Medicine</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3185,7 +3126,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="28.8" customHeight="1">
       <c r="A43" t="n">
         <v>42</v>
       </c>
@@ -3194,7 +3135,7 @@
           <t>s13054-026-06111-9.pdf</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>The effects of mechanical ventilation during v-a ecmo support: a systematic review</t>
         </is>
@@ -3216,7 +3157,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CVS / Pulmonology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3250,7 +3191,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="43.2" customHeight="1">
       <c r="A44" t="n">
         <v>43</v>
       </c>
@@ -3259,7 +3200,7 @@
           <t>diagnostic_and_prognostic_value_of_the_venous.875.pdf</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Diagnostic and Prognostic Value of the Venous Excess Ultrasound Grading System: A Systematic Review and Meta-Analysis</t>
         </is>
@@ -3281,7 +3222,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cardiovascular System (CVS) / Nephrology / Critical Care Ultrasound</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3315,7 +3256,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="43.2" customHeight="1">
       <c r="A45" t="n">
         <v>44</v>
       </c>
@@ -3324,7 +3265,7 @@
           <t>magnesium_sulfate_to_prevent_perioperative_atrial.847.pdf</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>Magnesium Sulfate to Prevent Perioperative Atrial Fibrillation in Cardiac Surgery: A Randomized Clinical Trial</t>
         </is>
@@ -3346,7 +3287,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cardiovascular System / Cardiothoracic Surgery</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3380,7 +3321,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="72" customHeight="1">
       <c r="A46" t="n">
         <v>45</v>
       </c>
@@ -3389,7 +3330,7 @@
           <t>PIIS103673142600041X.pdf</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>Heparinised saline versus normal saline flushing in maintaining arterial catheter patency in intensive care patients: A systematic review and meta-analysis of randomised controlled trials</t>
         </is>
@@ -3411,7 +3352,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Critical Care / Vascular Access</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3426,7 +3367,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3434,6 +3375,11 @@
           <t>2026-06-23 09:01:47</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:59:27</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Success</t>
@@ -3441,11 +3387,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="86.40000000000001" customHeight="1">
       <c r="A47" t="n">
         <v>46</v>
       </c>
@@ -3454,7 +3400,7 @@
           <t>s00134-026-08459-6.pdf</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>Personalized automatic management of tracheal cuff pressure and subglottic secretions drainage to prevent pneumonia in critically ill intubated patients. The MICROINHALO multicenter randomized controlled trial</t>
         </is>
@@ -3476,7 +3422,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pulmonology / Critical Care Medicine / Infectious Diseases</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3499,13 +3445,77 @@
           <t>2026-06-23 09:02:23</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>surviving_sepsis_campaign__international.5.pdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Surviving Sepsis Campaign: International Guidelines for Management of Sepsis and Septic Shock 2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Hallie C. Prescott, Massimo Antonelli, et al.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10.1097/CCM.0000000000007075</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:51:18</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RONAK\AI Projects\ai-microlearning - ACUMEN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482FF2B9-E006-4AE4-8B94-DFAFA528AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A30E59-C229-4D7F-BE63-43BA00042F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="390">
   <si>
     <t>Serial Number</t>
   </si>
@@ -923,6 +923,273 @@
   </si>
   <si>
     <t>2026-06-23 11:51:18</t>
+  </si>
+  <si>
+    <t>bmj-2025-084675.full.pdf</t>
+  </si>
+  <si>
+    <t>Effects of extreme heat on physiology, morbidity, and mortality under climate change: mechanisms and clinical implications</t>
+  </si>
+  <si>
+    <t>Jiayu Xu et al.</t>
+  </si>
+  <si>
+    <t>BMJ</t>
+  </si>
+  <si>
+    <t>10.1136/bmj-2025-084675</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:35:57</t>
+  </si>
+  <si>
+    <t>diagnostics-16-01548.pdf</t>
+  </si>
+  <si>
+    <t>Beyond the Tipping Point: Advances in the Diagnosis and Management of Acute-on-Chronic Liver Failure and End-Stage Liver Disease</t>
+  </si>
+  <si>
+    <t>Jonathan Soldera</t>
+  </si>
+  <si>
+    <t>Diagnostics</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/diagnostics16101548</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:36:43</t>
+  </si>
+  <si>
+    <t>evidence_based,_cost_effective_management_of_upper.3.pdf</t>
+  </si>
+  <si>
+    <t>Evidence-based, cost-effective management of upper gastrointestinal hemorrhage. An algorithm of the Journal of Trauma and Acute Care Surgery emergency general surgery algorithms work group</t>
+  </si>
+  <si>
+    <t>Todd W. Costantini, Kendall R. McEachron, et al.</t>
+  </si>
+  <si>
+    <t>10.1097/TA.0000000000005033</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:37:54</t>
+  </si>
+  <si>
+    <t>fimmu-14-1230049.pdf</t>
+  </si>
+  <si>
+    <t>Iatrogenic air embolism: pathoanatomy, thromboinflammation, endotheliopathy, and therapies</t>
+  </si>
+  <si>
+    <t>Phillip L. Marsh et al.</t>
+  </si>
+  <si>
+    <t>Frontiers in Immunology</t>
+  </si>
+  <si>
+    <t>10.3389/fimmu.2023.1230049</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:38:33</t>
+  </si>
+  <si>
+    <t>Flexible-bronchoscopy-in-.pdf</t>
+  </si>
+  <si>
+    <t>Flexible bronchoscopy in mechanically ventilated critically ill patients: practical considerations and clinical applications – a narrative review</t>
+  </si>
+  <si>
+    <t>Sylweriusz Kosiński et al.</t>
+  </si>
+  <si>
+    <t>Anaesthesiology Intensive Therapy</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5114/ait/218317</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:39:29</t>
+  </si>
+  <si>
+    <t>fmed-13-1808427.pdf</t>
+  </si>
+  <si>
+    <t>Comparative efficacy and safety of immunomodulatory therapies for sepsis: a systematic review and network meta-analysis</t>
+  </si>
+  <si>
+    <t>Luo R, et al.</t>
+  </si>
+  <si>
+    <t>10.3389/fmed.2026.1808427</t>
+  </si>
+  <si>
+    <t>Systematic Review and Network Meta-Analysis</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:39:58</t>
+  </si>
+  <si>
+    <t>jcm-15-04227.pdf</t>
+  </si>
+  <si>
+    <t>Central Venous Pressure Revisited: Physiology, Pitfalls, Misconceptions, and Modern Clinical Interpretation in Critical Care</t>
+  </si>
+  <si>
+    <t>Cesare Biuzzi et al.</t>
+  </si>
+  <si>
+    <t>10.3390/jcm15114227</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:40:26</t>
+  </si>
+  <si>
+    <t>neurolint-18-00085-v2.pdf</t>
+  </si>
+  <si>
+    <t>Early Versus Late Tracheostomy in Traumatic Spinal Injury: A Narrative Review</t>
+  </si>
+  <si>
+    <t>Saeed Mahmood et al.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/neurolint18050085</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:40:52</t>
+  </si>
+  <si>
+    <t>PIIS2950133426001102.pdf</t>
+  </si>
+  <si>
+    <t>Bridging strategies for heart-lung transplantation: Current concepts and mechanical support modalities</t>
+  </si>
+  <si>
+    <t>K. Hoetzenecker, J.W. Stokes, M. Bacchetta, and O. Mercier</t>
+  </si>
+  <si>
+    <t>JHLT Open</t>
+  </si>
+  <si>
+    <t>10.1016/j.jhlto.2026.100589</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:41:03</t>
+  </si>
+  <si>
+    <t>s10741-026-10636-0.pdf</t>
+  </si>
+  <si>
+    <t>Mineralocorticoid receptor antagonists for the treatment of heart failure and kidney disease: a state-of-the-art review</t>
+  </si>
+  <si>
+    <t>Harriette G. C. Van Spall et al.</t>
+  </si>
+  <si>
+    <t>Heart Failure Reviews</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10741-026-10636-0</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:41:57</t>
+  </si>
+  <si>
+    <t>s12028-026-02551-x.pdf</t>
+  </si>
+  <si>
+    <t>Rehabilitation in the Intensive Care Unit for Adults with Traumatic Brain Injury: A Systematic Review and Meta-analysis</t>
+  </si>
+  <si>
+    <t>Fiona Howroyd et al.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s12028-026-02551-x</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:42:31</t>
+  </si>
+  <si>
+    <t>s40001-026-04401-0.pdf</t>
+  </si>
+  <si>
+    <t>The gut–heart axis in sepsis-induced cardiomyopathy: pathophysiology, microbial metabolites, and cardiovascular insights</t>
+  </si>
+  <si>
+    <t>Zhaokai Li and Guoqiang Zhang</t>
+  </si>
+  <si>
+    <t>European Journal of Medical Research</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s40001-026-04401-0</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:43:06</t>
+  </si>
+  <si>
+    <t>UEG Journal - 2026 - Cárdenas‐Jaén - AEG‐AESPANC‐OPGE‐SIED‐SPG Ibero‐Latin American Guidelines on Acute Pancreatitis .pdf</t>
+  </si>
+  <si>
+    <t>AEG-AESPANC-OPGE-SIED-SPG Ibero-Latin American Guidelines on Acute Pancreatitis (iLATAM-AP)</t>
+  </si>
+  <si>
+    <t>Karina Cárdenas-Jaén et al.</t>
+  </si>
+  <si>
+    <t>United European Gastroenterology Journal</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/ueg2.70190</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:44:25</t>
+  </si>
+  <si>
+    <t>a-2725-7350.pdf</t>
+  </si>
+  <si>
+    <t>Pulmonary Infections in Patients with Human Immunodeficiency Virus Infection</t>
+  </si>
+  <si>
+    <t>Catia Cilloniz et al.</t>
+  </si>
+  <si>
+    <t>Seminars in Respiratory and Critical Care Medicine</t>
+  </si>
+  <si>
+    <t>10.1055/a-2725-7350</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:45:29</t>
+  </si>
+  <si>
+    <t>WJCCM-15-114264.pdf</t>
+  </si>
+  <si>
+    <t>Integrating structured point-of-care ultrasound into dengue fever management: A mini review and comprehensive clinical guide</t>
+  </si>
+  <si>
+    <t>Zhi-Yuan Lee et al.</t>
+  </si>
+  <si>
+    <t>World Journal of Critical Care Medicine</t>
+  </si>
+  <si>
+    <t>10.5492/wjccm.v15.i2.114264</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:47:00</t>
+  </si>
+  <si>
+    <t>Multisystem</t>
+  </si>
+  <si>
+    <t>Immunology</t>
+  </si>
+  <si>
+    <t>sepsis</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="39.88671875" style="1" customWidth="1"/>
@@ -1531,7 +1798,7 @@
         <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1572,7 +1839,7 @@
         <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1613,7 +1880,7 @@
         <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.3">
@@ -1654,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1695,7 +1962,7 @@
         <v>24</v>
       </c>
       <c r="N10" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1736,7 +2003,7 @@
         <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1777,7 +2044,7 @@
         <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1818,7 +2085,7 @@
         <v>24</v>
       </c>
       <c r="N13" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1903,7 +2170,7 @@
         <v>24</v>
       </c>
       <c r="N15" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1944,7 +2211,7 @@
         <v>24</v>
       </c>
       <c r="N16" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1985,7 +2252,7 @@
         <v>24</v>
       </c>
       <c r="N17" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2026,7 +2293,7 @@
         <v>24</v>
       </c>
       <c r="N18" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2067,7 +2334,7 @@
         <v>24</v>
       </c>
       <c r="N19" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -2108,7 +2375,7 @@
         <v>24</v>
       </c>
       <c r="N20" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2149,7 +2416,7 @@
         <v>24</v>
       </c>
       <c r="N21" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2190,7 +2457,7 @@
         <v>24</v>
       </c>
       <c r="N22" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2275,7 +2542,7 @@
         <v>24</v>
       </c>
       <c r="N24" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2316,7 +2583,7 @@
         <v>24</v>
       </c>
       <c r="N25" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2357,7 +2624,7 @@
         <v>24</v>
       </c>
       <c r="N26" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2398,7 +2665,7 @@
         <v>24</v>
       </c>
       <c r="N27" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2439,7 +2706,12 @@
         <v>24</v>
       </c>
       <c r="N28" t="s">
-        <v>53</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N29" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2480,7 +2752,7 @@
         <v>24</v>
       </c>
       <c r="N30" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2521,7 +2793,7 @@
         <v>24</v>
       </c>
       <c r="N31" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2562,7 +2834,7 @@
         <v>24</v>
       </c>
       <c r="N32" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2603,7 +2875,7 @@
         <v>24</v>
       </c>
       <c r="N33" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2644,7 +2916,7 @@
         <v>24</v>
       </c>
       <c r="N34" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2685,7 +2957,7 @@
         <v>24</v>
       </c>
       <c r="N35" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2726,7 +2998,7 @@
         <v>24</v>
       </c>
       <c r="N36" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2767,7 +3039,7 @@
         <v>24</v>
       </c>
       <c r="N37" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2808,7 +3080,7 @@
         <v>24</v>
       </c>
       <c r="N38" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2849,7 +3121,7 @@
         <v>24</v>
       </c>
       <c r="N39" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2890,7 +3162,7 @@
         <v>24</v>
       </c>
       <c r="N40" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2931,7 +3203,7 @@
         <v>24</v>
       </c>
       <c r="N41" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2972,7 +3244,7 @@
         <v>24</v>
       </c>
       <c r="N42" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3013,7 +3285,7 @@
         <v>24</v>
       </c>
       <c r="N43" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3054,7 +3326,7 @@
         <v>24</v>
       </c>
       <c r="N44" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3095,7 +3367,7 @@
         <v>24</v>
       </c>
       <c r="N45" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.3">
@@ -3180,7 +3452,7 @@
         <v>24</v>
       </c>
       <c r="N47" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -3221,7 +3493,628 @@
         <v>24</v>
       </c>
       <c r="N48" t="s">
-        <v>53</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>301</v>
+      </c>
+      <c r="C49" t="s">
+        <v>302</v>
+      </c>
+      <c r="D49" t="s">
+        <v>303</v>
+      </c>
+      <c r="E49" t="s">
+        <v>304</v>
+      </c>
+      <c r="F49" t="s">
+        <v>305</v>
+      </c>
+      <c r="G49" t="s">
+        <v>387</v>
+      </c>
+      <c r="H49" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>53</v>
+      </c>
+      <c r="K49" t="s">
+        <v>306</v>
+      </c>
+      <c r="M49" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>307</v>
+      </c>
+      <c r="C50" t="s">
+        <v>308</v>
+      </c>
+      <c r="D50" t="s">
+        <v>309</v>
+      </c>
+      <c r="E50" t="s">
+        <v>310</v>
+      </c>
+      <c r="F50" t="s">
+        <v>311</v>
+      </c>
+      <c r="G50" t="s">
+        <v>38</v>
+      </c>
+      <c r="H50" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>53</v>
+      </c>
+      <c r="K50" t="s">
+        <v>312</v>
+      </c>
+      <c r="M50" t="s">
+        <v>24</v>
+      </c>
+      <c r="N50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>313</v>
+      </c>
+      <c r="C51" t="s">
+        <v>314</v>
+      </c>
+      <c r="D51" t="s">
+        <v>315</v>
+      </c>
+      <c r="E51" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" t="s">
+        <v>316</v>
+      </c>
+      <c r="G51" t="s">
+        <v>73</v>
+      </c>
+      <c r="H51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>53</v>
+      </c>
+      <c r="K51" t="s">
+        <v>317</v>
+      </c>
+      <c r="M51" t="s">
+        <v>24</v>
+      </c>
+      <c r="N51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>318</v>
+      </c>
+      <c r="C52" t="s">
+        <v>319</v>
+      </c>
+      <c r="D52" t="s">
+        <v>320</v>
+      </c>
+      <c r="E52" t="s">
+        <v>321</v>
+      </c>
+      <c r="F52" t="s">
+        <v>322</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>53</v>
+      </c>
+      <c r="K52" t="s">
+        <v>323</v>
+      </c>
+      <c r="M52" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>324</v>
+      </c>
+      <c r="C53" t="s">
+        <v>325</v>
+      </c>
+      <c r="D53" t="s">
+        <v>326</v>
+      </c>
+      <c r="E53" t="s">
+        <v>327</v>
+      </c>
+      <c r="F53" t="s">
+        <v>328</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>53</v>
+      </c>
+      <c r="K53" t="s">
+        <v>329</v>
+      </c>
+      <c r="M53" t="s">
+        <v>24</v>
+      </c>
+      <c r="N53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>330</v>
+      </c>
+      <c r="C54" t="s">
+        <v>331</v>
+      </c>
+      <c r="D54" t="s">
+        <v>332</v>
+      </c>
+      <c r="E54" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" t="s">
+        <v>333</v>
+      </c>
+      <c r="G54" t="s">
+        <v>388</v>
+      </c>
+      <c r="H54" t="s">
+        <v>334</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>53</v>
+      </c>
+      <c r="K54" t="s">
+        <v>335</v>
+      </c>
+      <c r="M54" t="s">
+        <v>24</v>
+      </c>
+      <c r="N54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>336</v>
+      </c>
+      <c r="C55" t="s">
+        <v>337</v>
+      </c>
+      <c r="D55" t="s">
+        <v>338</v>
+      </c>
+      <c r="E55" t="s">
+        <v>101</v>
+      </c>
+      <c r="F55" t="s">
+        <v>339</v>
+      </c>
+      <c r="G55" t="s">
+        <v>150</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>53</v>
+      </c>
+      <c r="K55" t="s">
+        <v>340</v>
+      </c>
+      <c r="M55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>341</v>
+      </c>
+      <c r="C56" t="s">
+        <v>342</v>
+      </c>
+      <c r="D56" t="s">
+        <v>343</v>
+      </c>
+      <c r="E56" t="s">
+        <v>108</v>
+      </c>
+      <c r="F56" t="s">
+        <v>344</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>53</v>
+      </c>
+      <c r="K56" t="s">
+        <v>345</v>
+      </c>
+      <c r="M56" t="s">
+        <v>24</v>
+      </c>
+      <c r="N56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>346</v>
+      </c>
+      <c r="C57" t="s">
+        <v>347</v>
+      </c>
+      <c r="D57" t="s">
+        <v>348</v>
+      </c>
+      <c r="E57" t="s">
+        <v>349</v>
+      </c>
+      <c r="F57" t="s">
+        <v>350</v>
+      </c>
+      <c r="G57" t="s">
+        <v>150</v>
+      </c>
+      <c r="H57" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>53</v>
+      </c>
+      <c r="K57" t="s">
+        <v>351</v>
+      </c>
+      <c r="M57" t="s">
+        <v>24</v>
+      </c>
+      <c r="N57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>352</v>
+      </c>
+      <c r="C58" t="s">
+        <v>353</v>
+      </c>
+      <c r="D58" t="s">
+        <v>354</v>
+      </c>
+      <c r="E58" t="s">
+        <v>355</v>
+      </c>
+      <c r="F58" t="s">
+        <v>356</v>
+      </c>
+      <c r="G58" t="s">
+        <v>150</v>
+      </c>
+      <c r="H58" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>53</v>
+      </c>
+      <c r="K58" t="s">
+        <v>357</v>
+      </c>
+      <c r="M58" t="s">
+        <v>24</v>
+      </c>
+      <c r="N58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>358</v>
+      </c>
+      <c r="C59" t="s">
+        <v>359</v>
+      </c>
+      <c r="D59" t="s">
+        <v>360</v>
+      </c>
+      <c r="E59" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59" t="s">
+        <v>361</v>
+      </c>
+      <c r="G59" t="s">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>53</v>
+      </c>
+      <c r="K59" t="s">
+        <v>362</v>
+      </c>
+      <c r="M59" t="s">
+        <v>24</v>
+      </c>
+      <c r="N59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>363</v>
+      </c>
+      <c r="C60" t="s">
+        <v>364</v>
+      </c>
+      <c r="D60" t="s">
+        <v>365</v>
+      </c>
+      <c r="E60" t="s">
+        <v>366</v>
+      </c>
+      <c r="F60" t="s">
+        <v>367</v>
+      </c>
+      <c r="G60" t="s">
+        <v>150</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>53</v>
+      </c>
+      <c r="K60" t="s">
+        <v>368</v>
+      </c>
+      <c r="M60" t="s">
+        <v>24</v>
+      </c>
+      <c r="N60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>369</v>
+      </c>
+      <c r="C61" t="s">
+        <v>370</v>
+      </c>
+      <c r="D61" t="s">
+        <v>371</v>
+      </c>
+      <c r="E61" t="s">
+        <v>372</v>
+      </c>
+      <c r="F61" t="s">
+        <v>373</v>
+      </c>
+      <c r="G61" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" t="s">
+        <v>74</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>53</v>
+      </c>
+      <c r="K61" t="s">
+        <v>374</v>
+      </c>
+      <c r="M61" t="s">
+        <v>24</v>
+      </c>
+      <c r="N61" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>375</v>
+      </c>
+      <c r="C62" t="s">
+        <v>376</v>
+      </c>
+      <c r="D62" t="s">
+        <v>377</v>
+      </c>
+      <c r="E62" t="s">
+        <v>378</v>
+      </c>
+      <c r="F62" t="s">
+        <v>379</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>53</v>
+      </c>
+      <c r="K62" t="s">
+        <v>380</v>
+      </c>
+      <c r="M62" t="s">
+        <v>24</v>
+      </c>
+      <c r="N62" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C63"/>
+      <c r="N63" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>381</v>
+      </c>
+      <c r="C64" t="s">
+        <v>382</v>
+      </c>
+      <c r="D64" t="s">
+        <v>383</v>
+      </c>
+      <c r="E64" t="s">
+        <v>384</v>
+      </c>
+      <c r="F64" t="s">
+        <v>385</v>
+      </c>
+      <c r="G64" t="s">
+        <v>389</v>
+      </c>
+      <c r="H64" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>53</v>
+      </c>
+      <c r="K64" t="s">
+        <v>386</v>
+      </c>
+      <c r="M64" t="s">
+        <v>24</v>
+      </c>
+      <c r="N64" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -4506,41 +4506,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>surviving_sepsis_campaign__international.5.pdf</t>
+          <t>1-s2.0-S2772963X26002577-main.pdf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Surviving Sepsis Campaign: International Guidelines for Management of Sepsis and Septic Shock 2026</t>
+          <t>The Effect of Restrictive vs Liberal Blood Transfusion Strategy on Subsequent Myocardial Infarction Type</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Hallie C. Prescott et al.</t>
+          <t>Andrew P. DeFilippis et al.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Critical Care Medicine</t>
+          <t>JACC: ADVANCES</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.1097/CCM.0000000000007075</t>
+          <t>10.1016/j.jacadv.2026.102836</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Guideline</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-06-25 12:00:59</t>
+          <t>2026-06-25 13:09:43</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4571,41 +4571,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1-s2.0-S2772963X26002577-main.pdf</t>
+          <t>dexmedetomidine_versus_usual_care_in_adult.10.pdf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>The Effect of Restrictive vs Liberal Blood Transfusion Strategy on Subsequent Myocardial Infarction Type</t>
+          <t>Dexmedetomidine versus usual care in adult patients with septic shock receiving vasopressors: A systematic review and meta-analysis of randomised controlled trials</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Andrew P. DeFilippis et al.</t>
+          <t>Isaac B. Wolfkind et al.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>JACC: ADVANCES</t>
+          <t>Eur J Anaesthesiol Intensive Care Med</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10.1016/j.jacadv.2026.102836</t>
+          <t>10.1097/EA9.0000000000000113</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-06-25 13:09:43</t>
+          <t>2026-06-25 13:10:07</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4636,41 +4636,41 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>dexmedetomidine_versus_usual_care_in_adult.10.pdf</t>
+          <t>prabhakaran-et-al-2026-2026-guideline-for-the-early-management-of-patients-with-acute-ischemic-stroke-a-guideline-from.pdf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dexmedetomidine versus usual care in adult patients with septic shock receiving vasopressors: A systematic review and meta-analysis of randomised controlled trials</t>
+          <t>2026 Guideline for the Early Management of Patients With Acute Ischemic Stroke: A Guideline From the American Heart Association/American Stroke Association</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Isaac B. Wolfkind et al.</t>
+          <t>Shyam Prabhakaran et al.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eur J Anaesthesiol Intensive Care Med</t>
+          <t>Stroke</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10.1097/EA9.0000000000000113</t>
+          <t>10.1161/STR.0000000000000513</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>Guideline</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-06-25 13:10:07</t>
+          <t>2026-06-25 13:14:09</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4705,32 +4705,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>prabhakaran-et-al-2026-2026-guideline-for-the-early-management-of-patients-with-acute-ischemic-stroke-a-guideline-from.pdf</t>
+          <t>surviving_sepsis_campaign__international.5.pdf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026 Guideline for the Early Management of Patients With Acute Ischemic Stroke: A Guideline From the American Heart Association/American Stroke Association</t>
+          <t>Surviving Sepsis Campaign: International Guidelines for Management of Sepsis and Septic Shock 2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Shyam Prabhakaran et al.</t>
+          <t>Hallie C. Prescott et al.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stroke</t>
+          <t>Critical Care Medicine</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10.1161/STR.0000000000000513</t>
+          <t>10.1097/CCM.0000000000007075</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-06-25 13:14:09</t>
+          <t>2026-06-25 13:49:42</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="44.6640625" customWidth="1" min="2" max="2"/>
@@ -4753,13 +4753,143 @@
           <t>2026-06-25 13:49:42</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>blood_bld-2023-022899-c-main.pdf</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>How I diagnose and treat cardiorespiratory complications of transfusion</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>A. P. J. Vlaar et al.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Blood</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10.1182/blood.2023022899</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hematology</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:47:56</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>advpub_CJ-25-0987.pdf</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>JCS 2026 Guideline on the Management of Infective Endocarditis</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Chisato Izumi et al.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Circulation Journal</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10.1253/circj.CJ-25-0987</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:49:28</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -8,7 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry Logs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registry Logs'!$A$1:$N$67</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -415,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="44.6640625" customWidth="1" min="2" max="2"/>
@@ -2087,43 +2089,43 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="57.6" customHeight="1">
+    <row r="26" ht="43.2" customHeight="1">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>s12028-023-01752-y.pdf</t>
+          <t>s12245-025-01078-w.pdf</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Practice Guidance for the Critical Care Management of SAH: Intracranial Pressure Monitoring and Management in Aneurysmal Subarachnoid Hemorrhage</t>
+          <t>A narrative review of the diabetic ketoacidosis and hyperosmolar hyperglycemic state overlap syndrome</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Alberto Addis, Marta Baggiani, and Giuseppe Citerio</t>
+          <t>Eslam Abady, Panos I. Tamvakologos, Marina Ramzy Mourid, et al.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neurocritical Care</t>
+          <t>International Journal of Emergency Medicine</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10.1007/s12028-023-01752-y</t>
+          <t>10.1186/s12245-025-01078-w</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Guideline</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2138,7 +2140,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-06-21 15:42:29</t>
+          <t>2026-06-21 15:42:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2154,36 +2156,36 @@
     </row>
     <row r="27" ht="43.2" customHeight="1">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>s12245-025-01078-w.pdf</t>
+          <t>s15010-026-02852-5.pdf</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>A narrative review of the diabetic ketoacidosis and hyperosmolar hyperglycemic state overlap syndrome</t>
+          <t>The evolution of sepsis care: from protocol-driven management to personalized intensive care</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Eslam Abady, Panos I. Tamvakologos, Marina Ramzy Mourid, et al.</t>
+          <t>Tim Rahmel et al.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>International Journal of Emergency Medicine</t>
+          <t>Infection</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.1186/s12245-025-01078-w</t>
+          <t>10.1007/s15010-026-02852-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Endocrinology</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2203,7 +2205,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-06-21 15:42:37</t>
+          <t>2026-06-21 15:42:50</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2217,95 +2219,95 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="43.2" customHeight="1">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>s15010-026-02852-5.pdf</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>The evolution of sepsis care: from protocol-driven management to personalized intensive care</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Tim Rahmel et al.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Infection</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>10.1007/s15010-026-02852-5</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Sepsis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+    <row r="28">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>29</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Acute-confusion-in-pregnancy_2025_Clinical-Medicine.pdf</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>Acute confusion in pregnancy</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Amanda Hill et al.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.clinme.2024.100273</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Obstetrics and Gynecology</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2026-06-21 15:42:50</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:04:47</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="28.8" customHeight="1">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acute-confusion-in-pregnancy_2025_Clinical-Medicine.pdf</t>
+          <t>Approach-to-investigation-and-management-of-proteinuria-i_2025_Clinical-Medi.pdf</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Acute confusion in pregnancy</t>
+          <t>Approach to investigation and management of proteinuria in pregnancy</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Amanda Hill et al.</t>
+          <t>Isabela Bertoni, Sion Williams</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2315,7 +2317,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.clinme.2024.100273</t>
+          <t>10.1016/j.clinme.2024.100281</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2340,7 +2342,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-06-22 14:04:47</t>
+          <t>2026-06-22 14:05:35</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2356,21 +2358,21 @@
     </row>
     <row r="31" ht="28.8" customHeight="1">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Approach-to-investigation-and-management-of-proteinuria-i_2025_Clinical-Medi.pdf</t>
+          <t>Severe-acute-pulmonary-embolism-in-pregnancy_2025_Clinical-Medicine.pdf</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Approach to investigation and management of proteinuria in pregnancy</t>
+          <t>Severe acute pulmonary embolism in pregnancy</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Isabela Bertoni, Sion Williams</t>
+          <t>Bhaskar Narayan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2380,7 +2382,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10.1016/j.clinme.2024.100281</t>
+          <t>10.1016/j.clinme.2024.100274</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2405,7 +2407,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-06-22 14:05:35</t>
+          <t>2026-06-22 14:06:50</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2419,43 +2421,43 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="28.8" customHeight="1">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Management-of-asthma-in-pregnancy_2025_Clinical-Medicine.pdf</t>
+          <t>acc-000884.pdf</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Management of asthma in pregnancy</t>
+          <t>Managing sepsis in the era of precision medicine: a narrative review</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C.E. Jones et al.</t>
+          <t>Ho Jin Yong et al.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Clinical Medicine</t>
+          <t>Acute and Critical Care</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.1016/j.clinme.2024.100277</t>
+          <t>https://doi.org/10.4266/acc.000884</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynecology</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Guideline</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2470,7 +2472,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-06-22 14:05:57</t>
+          <t>2026-06-22 14:28:34</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2484,38 +2486,38 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="28.8" customHeight="1">
+    <row r="33" ht="43.2" customHeight="1">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Severe-acute-pulmonary-embolism-in-pregnancy_2025_Clinical-Medicine.pdf</t>
+          <t>acc-003425.pdf</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Severe acute pulmonary embolism in pregnancy</t>
+          <t>Beyond blood pressure: a comprehensive overview of clinical indices in shock and tissue hypoperfusion</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bhaskar Narayan</t>
+          <t>Jooyun Kim et al.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Clinical Medicine</t>
+          <t>Acute and Critical Care</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10.1016/j.clinme.2024.100274</t>
+          <t>https://doi.org/10.4266/acc.003425</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynecology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2535,7 +2537,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-06-22 14:06:50</t>
+          <t>2026-06-22 14:30:36</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2551,36 +2553,36 @@
     </row>
     <row r="34" ht="28.8" customHeight="1">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>acc-000884.pdf</t>
+          <t>current_management_of_traumatic_intracranial.1.pdf</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Managing sepsis in the era of precision medicine: a narrative review</t>
+          <t>Current management of traumatic intracranial hypertension: What you need to know</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ho Jin Yong et al.</t>
+          <t>Alex B. Valadka et al.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Acute and Critical Care</t>
+          <t>Journal of Trauma and Acute Care Surgery</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4266/acc.000884</t>
+          <t>10.1097/TA.0000000000004921</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2600,7 +2602,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:34</t>
+          <t>2026-06-22 14:33:25</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2614,33 +2616,33 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="43.2" customHeight="1">
+    <row r="35" ht="57.6" customHeight="1">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>acc-003425.pdf</t>
+          <t>s10877-026-01457-5.pdf</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Beyond blood pressure: a comprehensive overview of clinical indices in shock and tissue hypoperfusion</t>
+          <t>Echocardiography before non-cardiac surgery: current knowledge, guideline recommendations, and clinical evidence – a narrative review</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Jooyun Kim et al.</t>
+          <t>Viktoria Mertin, Alexandra Stroda, Tobias Bruns, Giovanna Lurati Buse</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Acute and Critical Care</t>
+          <t>Journal of Clinical Monitoring and Computing</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4266/acc.003425</t>
+          <t>10.1007/s10877-026-01457-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2665,7 +2667,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-06-22 14:30:36</t>
+          <t>2026-06-22 14:33:35</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2679,33 +2681,33 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="28.8" customHeight="1">
+    <row r="36" ht="57.6" customHeight="1">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>current_management_of_traumatic_intracranial.1.pdf</t>
+          <t>s12028-026-02565-5.pdf</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Current management of traumatic intracranial hypertension: What you need to know</t>
+          <t>Safety and Additive Efficacy of Dual CSF Drainage (Ventricular + Lumbar) in Severe Aneurysmal Subarachnoid Hemorrhage: A Secondary Analysis of the EARLYDRAIN Trial</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Alex B. Valadka et al.</t>
+          <t>Gianluca Trevisi, Matteo Palermo, et al.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Journal of Trauma and Acute Care Surgery</t>
+          <t>Neurocrit Care</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10.1097/TA.0000000000004921</t>
+          <t>10.1007/s12028-026-02565-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2730,7 +2732,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-06-22 14:33:25</t>
+          <t>2026-06-22 14:35:33</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2746,41 +2748,41 @@
     </row>
     <row r="37" ht="57.6" customHeight="1">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>s10877-026-01457-5.pdf</t>
+          <t>s13054-026-06142-2_reference.pdf</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Echocardiography before non-cardiac surgery: current knowledge, guideline recommendations, and clinical evidence – a narrative review</t>
+          <t>Comparative efficacy and safety of extended versus continuous infusion of beta-lactam antibiotics for severe infection: a network meta-analysis of randomized trials</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Viktoria Mertin, Alexandra Stroda, Tobias Bruns, Giovanna Lurati Buse</t>
+          <t>Zhou L. et al.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Journal of Clinical Monitoring and Computing</t>
+          <t>Critical Care</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.1007/s10877-026-01457-5</t>
+          <t>https://doi.org/10.1186/s13054-026-06142-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2795,7 +2797,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-06-22 14:33:35</t>
+          <t>2026-06-22 14:36:34</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2811,108 +2813,108 @@
     </row>
     <row r="38" ht="57.6" customHeight="1">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>s12028-026-02565-5.pdf</t>
+          <t>s13054-026-06144-0.pdf</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Safety and Additive Efficacy of Dual CSF Drainage (Ventricular + Lumbar) in Severe Aneurysmal Subarachnoid Hemorrhage: A Secondary Analysis of the EARLYDRAIN Trial</t>
+          <t>Implementation of the kidney protection strategy in critically ill patients with acute kidney injury – a multi-center prospective cohort study</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gianluca Trevisi, Matteo Palermo, et al.</t>
+          <t>Mahan Sadjadi et al.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neurocrit Care</t>
+          <t>Critical Care</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10.1007/s12028-026-02565-5</t>
+          <t>https://doi.org/10.1186/s13054-026-06144-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:37:21</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28.8" customHeight="1">
+      <c r="A39" t="n">
+        <v>40</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2667100X26001180-main.pdf</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>The potential role of methylene blue as an adjunctive therapy in septic shock</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Xinxin Cui, Jian Song, et al.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Journal of Intensive Medicine</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10.1016/j.jointm.2026.05.002</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sepsis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2026-06-22 14:35:33</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="57.6" customHeight="1">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>s13054-026-06142-2_reference.pdf</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>Comparative efficacy and safety of extended versus continuous infusion of beta-lactam antibiotics for severe infection: a network meta-analysis of randomized trials</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Zhou L. et al.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Critical Care</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1186/s13054-026-06142-2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Infectious Diseases</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Meta-analysis</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2925,7 +2927,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-06-22 14:36:34</t>
+          <t>2026-06-23 08:03:19</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2939,43 +2941,43 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="57.6" customHeight="1">
+    <row r="40" ht="43.2" customHeight="1">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>s13054-026-06144-0.pdf</t>
+          <t>jcm-15-04453.pdf</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Implementation of the kidney protection strategy in critically ill patients with acute kidney injury – a multi-center prospective cohort study</t>
+          <t>Mechanical Support in Myocardial Infarction Complicated by Cardiogenic Shock: What Have We Learned from Trials?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mahan Sadjadi et al.</t>
+          <t>Cristina Aurigemma et al.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Critical Care</t>
+          <t>Journal of Clinical Medicine</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s13054-026-06144-0</t>
+          <t>https://doi.org/10.3390/jcm15124453</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephrology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2990,7 +2992,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-06-22 14:37:21</t>
+          <t>2026-06-23 08:31:53</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3006,36 +3008,36 @@
     </row>
     <row r="41" ht="28.8" customHeight="1">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1-s2.0-S2667100X26001180-main.pdf</t>
+          <t>s13054-026-06111-9.pdf</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>The potential role of methylene blue as an adjunctive therapy in septic shock</t>
+          <t>The effects of mechanical ventilation during v-a ecmo support: a systematic review</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Xinxin Cui, Jian Song, et al.</t>
+          <t>Ilaria Protti et al.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Journal of Intensive Medicine</t>
+          <t>Critical Care</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10.1016/j.jointm.2026.05.002</t>
+          <t>https://doi.org/10.1186/s13054-026-06111-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3055,7 +3057,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-06-23 08:03:19</t>
+          <t>2026-06-23 08:32:23</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3071,31 +3073,31 @@
     </row>
     <row r="42" ht="43.2" customHeight="1">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jcm-15-04453.pdf</t>
+          <t>diagnostic_and_prognostic_value_of_the_venous.875.pdf</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Mechanical Support in Myocardial Infarction Complicated by Cardiogenic Shock: What Have We Learned from Trials?</t>
+          <t>Diagnostic and Prognostic Value of the Venous Excess Ultrasound Grading System: A Systematic Review and Meta-Analysis</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cristina Aurigemma et al.</t>
+          <t>Peter Klompmaker et al.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Journal of Clinical Medicine</t>
+          <t>Critical Care Medicine</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/jcm15124453</t>
+          <t>10.1097/CCM.0000000000007219</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3120,7 +3122,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-06-23 08:31:53</t>
+          <t>2026-06-23 08:32:56</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3134,331 +3136,331 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="28.8" customHeight="1">
+    <row r="43" ht="43.2" customHeight="1">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>s13054-026-06111-9.pdf</t>
+          <t>magnesium_sulfate_to_prevent_perioperative_atrial.847.pdf</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>The effects of mechanical ventilation during v-a ecmo support: a systematic review</t>
+          <t>Magnesium Sulfate to Prevent Perioperative Atrial Fibrillation in Cardiac Surgery: A Randomized Clinical Trial</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ilaria Protti et al.</t>
+          <t>Manon Meerman, MD et al.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Critical Care</t>
+          <t>Critical Care Medicine</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s13054-026-06111-9</t>
+          <t>10.1097/CCM.0000000000007162</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:00:57</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="72" customHeight="1">
+      <c r="A44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PIIS103673142600041X.pdf</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Heparinised saline versus normal saline flushing in maintaining arterial catheter patency in intensive care patients: A systematic review and meta-analysis of randomised controlled trials</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Guglielmo Imbriaco, RN, MSN, Lorenzo Gamberini, MD, et al.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Australian Critical Care</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10.1016/j.aucc.2026.101571</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:01:47</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:59:27</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="86.40000000000001" customHeight="1">
+      <c r="A45" t="n">
+        <v>46</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>s00134-026-08459-6.pdf</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Personalized automatic management of tracheal cuff pressure and subglottic secretions drainage to prevent pneumonia in critically ill intubated patients. The MICROINHALO multicenter randomized controlled trial</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>De Pascale et al.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Intensive Care Medicine</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00134-026-08459-6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>Pulmonology</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:02:23</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>48</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>bmj-2025-084675.full.pdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Effects of extreme heat on physiology, morbidity, and mortality under climate change: mechanisms and clinical implications</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jiayu Xu et al.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BMJ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10.1136/bmj-2025-084675</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Multisystem</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2026-06-23 08:32:23</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="43.2" customHeight="1">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>diagnostic_and_prognostic_value_of_the_venous.875.pdf</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>Diagnostic and Prognostic Value of the Venous Excess Ultrasound Grading System: A Systematic Review and Meta-Analysis</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Peter Klompmaker et al.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Critical Care Medicine</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>10.1097/CCM.0000000000007219</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:35:57</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>49</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>diagnostics-16-01548.pdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Beyond the Tipping Point: Advances in the Diagnosis and Management of Acute-on-Chronic Liver Failure and End-Stage Liver Disease</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Jonathan Soldera</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/diagnostics16101548</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2026-06-23 08:32:56</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="43.2" customHeight="1">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>magnesium_sulfate_to_prevent_perioperative_atrial.847.pdf</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Magnesium Sulfate to Prevent Perioperative Atrial Fibrillation in Cardiac Surgery: A Randomized Clinical Trial</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Manon Meerman, MD et al.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Critical Care Medicine</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>10.1097/CCM.0000000000007162</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Cardiology</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Trial</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2026-06-23 09:00:57</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="72" customHeight="1">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>PIIS103673142600041X.pdf</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>Heparinised saline versus normal saline flushing in maintaining arterial catheter patency in intensive care patients: A systematic review and meta-analysis of randomised controlled trials</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Guglielmo Imbriaco, RN, MSN, Lorenzo Gamberini, MD, et al.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Australian Critical Care</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>10.1016/j.aucc.2026.101571</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>2026-06-23 09:01:47</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2026-06-23 11:59:27</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="86.40000000000001" customHeight="1">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>s00134-026-08459-6.pdf</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>Personalized automatic management of tracheal cuff pressure and subglottic secretions drainage to prevent pneumonia in critically ill intubated patients. The MICROINHALO multicenter randomized controlled trial</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>De Pascale et al.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Intensive Care Medicine</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s00134-026-08459-6</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Pulmonology</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Trial</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2026-06-23 09:02:23</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:36:43</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3466,41 +3468,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>bmj-2025-084675.full.pdf</t>
+          <t>evidence_based,_cost_effective_management_of_upper.3.pdf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Effects of extreme heat on physiology, morbidity, and mortality under climate change: mechanisms and clinical implications</t>
+          <t>Evidence-based, cost-effective management of upper gastrointestinal hemorrhage. An algorithm of the Journal of Trauma and Acute Care Surgery emergency general surgery algorithms work group</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jiayu Xu et al.</t>
+          <t>Todd W. Costantini, Kendall R. McEachron, et al.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BMJ</t>
+          <t>Journal of Trauma and Acute Care Surgery</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10.1136/bmj-2025-084675</t>
+          <t>10.1097/TA.0000000000005033</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Multisystem</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Guideline</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3515,7 +3517,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-06-25 08:35:57</t>
+          <t>2026-06-25 08:37:54</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3531,36 +3533,36 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>diagnostics-16-01548.pdf</t>
+          <t>fimmu-14-1230049.pdf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beyond the Tipping Point: Advances in the Diagnosis and Management of Acute-on-Chronic Liver Failure and End-Stage Liver Disease</t>
+          <t>Iatrogenic air embolism: pathoanatomy, thromboinflammation, endotheliopathy, and therapies</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Jonathan Soldera</t>
+          <t>Phillip L. Marsh et al.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Diagnostics</t>
+          <t>Frontiers in Immunology</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/diagnostics16101548</t>
+          <t>10.3389/fimmu.2023.1230049</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3580,7 +3582,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-06-25 08:36:43</t>
+          <t>2026-06-25 08:38:33</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3596,41 +3598,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>evidence_based,_cost_effective_management_of_upper.3.pdf</t>
+          <t>Flexible-bronchoscopy-in-.pdf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Evidence-based, cost-effective management of upper gastrointestinal hemorrhage. An algorithm of the Journal of Trauma and Acute Care Surgery emergency general surgery algorithms work group</t>
+          <t>Flexible bronchoscopy in mechanically ventilated critically ill patients: practical considerations and clinical applications – a narrative review</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Todd W. Costantini, Kendall R. McEachron, et al.</t>
+          <t>Sylweriusz Kosiński et al.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Journal of Trauma and Acute Care Surgery</t>
+          <t>Anaesthesiology Intensive Therapy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10.1097/TA.0000000000005033</t>
+          <t>https://doi.org/10.5114/ait/218317</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Guideline</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3645,7 +3647,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-06-25 08:37:54</t>
+          <t>2026-06-25 08:39:29</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3661,41 +3663,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fimmu-14-1230049.pdf</t>
+          <t>fmed-13-1808427.pdf</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Iatrogenic air embolism: pathoanatomy, thromboinflammation, endotheliopathy, and therapies</t>
+          <t>Comparative efficacy and safety of immunomodulatory therapies for sepsis: a systematic review and network meta-analysis</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Phillip L. Marsh et al.</t>
+          <t>Luo R, et al.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Frontiers in Immunology</t>
+          <t>Frontiers in Medicine</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10.3389/fimmu.2023.1230049</t>
+          <t>10.3389/fmed.2026.1808427</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Immunology</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3710,7 +3712,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-06-25 08:38:33</t>
+          <t>2026-06-25 08:39:58</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3726,36 +3728,36 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Flexible-bronchoscopy-in-.pdf</t>
+          <t>jcm-15-04227.pdf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Flexible bronchoscopy in mechanically ventilated critically ill patients: practical considerations and clinical applications – a narrative review</t>
+          <t>Central Venous Pressure Revisited: Physiology, Pitfalls, Misconceptions, and Modern Clinical Interpretation in Critical Care</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sylweriusz Kosiński et al.</t>
+          <t>Cesare Biuzzi et al.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Anaesthesiology Intensive Therapy</t>
+          <t>Journal of Clinical Medicine</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5114/ait/218317</t>
+          <t>10.3390/jcm15114227</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3775,7 +3777,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-06-25 08:39:29</t>
+          <t>2026-06-25 08:40:26</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3791,41 +3793,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>fmed-13-1808427.pdf</t>
+          <t>neurolint-18-00085-v2.pdf</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Comparative efficacy and safety of immunomodulatory therapies for sepsis: a systematic review and network meta-analysis</t>
+          <t>Early Versus Late Tracheostomy in Traumatic Spinal Injury: A Narrative Review</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Luo R, et al.</t>
+          <t>Saeed Mahmood et al.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Frontiers in Medicine</t>
+          <t>Neurology International</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10.3389/fmed.2026.1808427</t>
+          <t>https://doi.org/10.3390/neurolint18050085</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Immunology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3840,7 +3842,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-06-25 08:39:58</t>
+          <t>2026-06-25 08:40:52</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3856,31 +3858,31 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jcm-15-04227.pdf</t>
+          <t>PIIS2950133426001102.pdf</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Central Venous Pressure Revisited: Physiology, Pitfalls, Misconceptions, and Modern Clinical Interpretation in Critical Care</t>
+          <t>Bridging strategies for heart-lung transplantation: Current concepts and mechanical support modalities</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cesare Biuzzi et al.</t>
+          <t>K. Hoetzenecker, J.W. Stokes, M. Bacchetta, and O. Mercier</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Journal of Clinical Medicine</t>
+          <t>JHLT Open</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10.3390/jcm15114227</t>
+          <t>10.1016/j.jhlto.2026.100589</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3905,7 +3907,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-06-25 08:40:26</t>
+          <t>2026-06-25 08:41:03</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3921,36 +3923,36 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>neurolint-18-00085-v2.pdf</t>
+          <t>s10741-026-10636-0.pdf</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Early Versus Late Tracheostomy in Traumatic Spinal Injury: A Narrative Review</t>
+          <t>Mineralocorticoid receptor antagonists for the treatment of heart failure and kidney disease: a state-of-the-art review</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Saeed Mahmood et al.</t>
+          <t>Harriette G. C. Van Spall et al.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neurology International</t>
+          <t>Heart Failure Reviews</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/neurolint18050085</t>
+          <t>https://doi.org/10.1007/s10741-026-10636-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3970,7 +3972,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-06-25 08:40:52</t>
+          <t>2026-06-25 08:41:57</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3986,36 +3988,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PIIS2950133426001102.pdf</t>
+          <t>s12028-026-02551-x.pdf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bridging strategies for heart-lung transplantation: Current concepts and mechanical support modalities</t>
+          <t>Rehabilitation in the Intensive Care Unit for Adults with Traumatic Brain Injury: A Systematic Review and Meta-analysis</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>K. Hoetzenecker, J.W. Stokes, M. Bacchetta, and O. Mercier</t>
+          <t>Fiona Howroyd et al.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JHLT Open</t>
+          <t>Neurocritical Care</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10.1016/j.jhlto.2026.100589</t>
+          <t>https://doi.org/10.1007/s12028-026-02551-x</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4035,7 +4037,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-06-25 08:41:03</t>
+          <t>2026-06-25 08:42:31</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4051,31 +4053,31 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>s10741-026-10636-0.pdf</t>
+          <t>s40001-026-04401-0.pdf</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mineralocorticoid receptor antagonists for the treatment of heart failure and kidney disease: a state-of-the-art review</t>
+          <t>The gut–heart axis in sepsis-induced cardiomyopathy: pathophysiology, microbial metabolites, and cardiovascular insights</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Harriette G. C. Van Spall et al.</t>
+          <t>Zhaokai Li and Guoqiang Zhang</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heart Failure Reviews</t>
+          <t>European Journal of Medical Research</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s10741-026-10636-0</t>
+          <t>https://doi.org/10.1186/s40001-026-04401-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4100,7 +4102,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-06-25 08:41:57</t>
+          <t>2026-06-25 08:43:06</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4116,41 +4118,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>s12028-026-02551-x.pdf</t>
+          <t>UEG Journal - 2026 - Cárdenas‐Jaén - AEG‐AESPANC‐OPGE‐SIED‐SPG Ibero‐Latin American Guidelines on Acute Pancreatitis .pdf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rehabilitation in the Intensive Care Unit for Adults with Traumatic Brain Injury: A Systematic Review and Meta-analysis</t>
+          <t>AEG-AESPANC-OPGE-SIED-SPG Ibero-Latin American Guidelines on Acute Pancreatitis (iLATAM-AP)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fiona Howroyd et al.</t>
+          <t>Karina Cárdenas-Jaén et al.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Neurocritical Care</t>
+          <t>United European Gastroenterology Journal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s12028-026-02551-x</t>
+          <t>https://doi.org/10.1002/ueg2.70190</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Guideline</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4165,7 +4167,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-06-25 08:42:31</t>
+          <t>2026-06-25 08:44:25</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4181,36 +4183,36 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>s40001-026-04401-0.pdf</t>
+          <t>a-2725-7350.pdf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The gut–heart axis in sepsis-induced cardiomyopathy: pathophysiology, microbial metabolites, and cardiovascular insights</t>
+          <t>Pulmonary Infections in Patients with Human Immunodeficiency Virus Infection</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Zhaokai Li and Guoqiang Zhang</t>
+          <t>Catia Cilloniz et al.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>European Journal of Medical Research</t>
+          <t>Seminars in Respiratory and Critical Care Medicine</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s40001-026-04401-0</t>
+          <t>10.1055/a-2725-7350</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4230,7 +4232,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-06-25 08:43:06</t>
+          <t>2026-06-25 08:45:29</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4246,41 +4248,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UEG Journal - 2026 - Cárdenas‐Jaén - AEG‐AESPANC‐OPGE‐SIED‐SPG Ibero‐Latin American Guidelines on Acute Pancreatitis .pdf</t>
+          <t>WJCCM-15-114264.pdf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AEG-AESPANC-OPGE-SIED-SPG Ibero-Latin American Guidelines on Acute Pancreatitis (iLATAM-AP)</t>
+          <t>Integrating structured point-of-care ultrasound into dengue fever management: A mini review and comprehensive clinical guide</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Karina Cárdenas-Jaén et al.</t>
+          <t>Zhi-Yuan Lee et al.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United European Gastroenterology Journal</t>
+          <t>World Journal of Critical Care Medicine</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/ueg2.70190</t>
+          <t>10.5492/wjccm.v15.i2.114264</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Guideline</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4295,7 +4297,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-06-25 08:44:25</t>
+          <t>2026-06-25 08:47:00</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4311,36 +4313,36 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>a-2725-7350.pdf</t>
+          <t>rapid_microbiological_diagnostics_for_sepsis_.6.pdf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pulmonary Infections in Patients with Human Immunodeficiency Virus Infection</t>
+          <t>Rapid Microbiological Diagnostics for Sepsis: Narrative Review of Current and Prospective Approaches</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Catia Cilloniz et al.</t>
+          <t>Luke B. Harrison et al.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Seminars in Respiratory and Critical Care Medicine</t>
+          <t>Critical Care Explorations</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10.1055/a-2725-7350</t>
+          <t>10.1097/CCE.0000000000001415</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Sepsis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4360,7 +4362,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-06-25 08:45:29</t>
+          <t>2026-06-25 11:59:49</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4370,47 +4372,47 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WJCCM-15-114264.pdf</t>
+          <t>1-s2.0-S2772963X26002577-main.pdf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Integrating structured point-of-care ultrasound into dengue fever management: A mini review and comprehensive clinical guide</t>
+          <t>The Effect of Restrictive vs Liberal Blood Transfusion Strategy on Subsequent Myocardial Infarction Type</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Zhi-Yuan Lee et al.</t>
+          <t>Andrew P. DeFilippis et al.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>World Journal of Critical Care Medicine</t>
+          <t>JACC: ADVANCES</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10.5492/wjccm.v15.i2.114264</t>
+          <t>10.1016/j.jacadv.2026.102836</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4425,7 +4427,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-06-25 08:47:00</t>
+          <t>2026-06-25 13:09:43</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4435,37 +4437,37 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>rapid_microbiological_diagnostics_for_sepsis_.6.pdf</t>
+          <t>dexmedetomidine_versus_usual_care_in_adult.10.pdf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rapid Microbiological Diagnostics for Sepsis: Narrative Review of Current and Prospective Approaches</t>
+          <t>Dexmedetomidine versus usual care in adult patients with septic shock receiving vasopressors: A systematic review and meta-analysis of randomised controlled trials</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Luke B. Harrison et al.</t>
+          <t>Isaac B. Wolfkind et al.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Critical Care Explorations</t>
+          <t>Eur J Anaesthesiol Intensive Care Med</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10.1097/CCE.0000000000001415</t>
+          <t>10.1097/EA9.0000000000000113</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4475,7 +4477,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Meta-analysis</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4490,7 +4492,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-06-25 11:59:49</t>
+          <t>2026-06-25 13:10:07</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4506,41 +4508,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1-s2.0-S2772963X26002577-main.pdf</t>
+          <t>blood_bld-2023-022899-c-main.pdf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The Effect of Restrictive vs Liberal Blood Transfusion Strategy on Subsequent Myocardial Infarction Type</t>
+          <t>How I diagnose and treat cardiorespiratory complications of transfusion</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Andrew P. DeFilippis et al.</t>
+          <t>A. P. J. Vlaar et al.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JACC: ADVANCES</t>
+          <t>Blood</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.1016/j.jacadv.2026.102836</t>
+          <t>10.1182/blood.2023022899</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4555,7 +4557,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-06-25 13:09:43</t>
+          <t>2026-06-26 11:47:56</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4571,41 +4573,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>dexmedetomidine_versus_usual_care_in_adult.10.pdf</t>
+          <t>advpub_CJ-25-0987.pdf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dexmedetomidine versus usual care in adult patients with septic shock receiving vasopressors: A systematic review and meta-analysis of randomised controlled trials</t>
+          <t>JCS 2026 Guideline on the Management of Infective Endocarditis</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Isaac B. Wolfkind et al.</t>
+          <t>Chisato Izumi et al.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eur J Anaesthesiol Intensive Care Med</t>
+          <t>Circulation Journal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10.1097/EA9.0000000000000113</t>
+          <t>10.1253/circj.CJ-25-0987</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>Guideline</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4620,7 +4622,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-06-25 13:10:07</t>
+          <t>2026-06-26 11:49:28</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4636,36 +4638,36 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>prabhakaran-et-al-2026-2026-guideline-for-the-early-management-of-patients-with-acute-ischemic-stroke-a-guideline-from.pdf</t>
+          <t>3.5flash_1-s2.0-S1875213626000513.pdf</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026 Guideline for the Early Management of Patients With Acute Ischemic Stroke: A Guideline From the American Heart Association/American Stroke Association</t>
+          <t>Experts’ recommendations for the management of adult patients with cardiogenic shock</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Shyam Prabhakaran et al.</t>
+          <t>Nadia Aissaoui et al.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stroke</t>
+          <t>Archives of Cardiovascular Disease</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10.1161/STR.0000000000000513</t>
+          <t>10.1016/j.acvd.2026.02.001</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4685,7 +4687,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-06-25 13:14:09</t>
+          <t>2026-06-26 12:04:39</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4705,32 +4707,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>surviving_sepsis_campaign__international.5.pdf</t>
+          <t>000549732.pdf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Surviving Sepsis Campaign: International Guidelines for Management of Sepsis and Septic Shock 2026</t>
+          <t>Clinical Guideline for Treating Acute Respiratory Insufficiency with Invasive Ventilation and Extracorporeal Membrane Oxygenation: Updated Evidence-Based Recommendations for Choosing Modes and Setting Parameters of Mechanical Ventilation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Hallie C. Prescott et al.</t>
+          <t>Friedrich Hohmann et al.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Critical Care Medicine</t>
+          <t>Respiration</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10.1097/CCM.0000000000007075</t>
+          <t>10.1159/000549732</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sepsis</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4750,7 +4752,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-06-25 13:49:42</t>
+          <t>2026-06-26 20:28:22</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4770,32 +4772,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>blood_bld-2023-022899-c-main.pdf</t>
+          <t>1-s2.0-S1470211824054629.pdf</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>How I diagnose and treat cardiorespiratory complications of transfusion</t>
+          <t>Management of asthma in pregnancy</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>A. P. J. Vlaar et al.</t>
+          <t>CE Jones et al.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Blood</t>
+          <t>Clinical Medicine</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10.1182/blood.2023022899</t>
+          <t>10.1016/j.clinme.2024.100277</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hematology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4815,7 +4817,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-06-26 11:47:56</t>
+          <t>2026-06-26 20:29:30</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4835,67 +4837,653 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>advpub_CJ-25-0987.pdf</t>
+          <t>1-s2.0-S2110582025020199-main.pdf</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>Guidelines for the Initial Assessment of Respiratory Distress in the Emergency Department</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>P. Le Borgne et al.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Annals of Intensive Care</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10.1016/j.aicoj.2025.100005</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:30:39</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1-s2.0-S2772529426000470.pdf</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>The management of severe isolated traumatic brain injury in pregnancy: A joint consensus statement from the European Association of Neurosurgical Societies (EANS) and the World Society of Emergency Surgery (WSES)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Edoardo Picetti et al.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Brain and Spine</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>10.1016/j.bas.2026.105971</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neurology</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:31:57</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025_elso_consensus_statement_for_the_provision.2.pdf</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025 ELSO Consensus Statement for the Provision and Management of Nutrition Therapy in Critically Ill Adult Patients Requiring Extracorporeal Membrane Oxygenation</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Danielle E. Bear et al.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ASAIO Journal</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10.1097/MAT.0000000000002657</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:33:21</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>advpub_CJ-25-0987 (1).pdf</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>JCS 2026 Guideline on the Management of Infective Endocarditis</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Chisato Izumi et al.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Circulation Journal</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>10.1253/circj.CJ-25-0987</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>Guideline</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:35:19</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>creager-et-al-2026-2026-aha-acc-accp-acep-chest-scai-shm-sir-svm-svn-guideline-for-the-evaluation-and-management-of.pdf</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026 AHA/ACC/ACCP/ACEP/CHEST/SCAI/SHM/SIR/SVM/SVN Guideline for the Evaluation and Management of Acute Pulmonary Embolism in Adults: A Report of the American College of Cardiology/American Heart Association Joint Committee on Clinical Practice Guidelines</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mark A. Creager et al.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Circulation</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10.1161/CIR.0000000000001415</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Multisystem</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>Guideline</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2026-06-26 11:49:28</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:37:07</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>dennis-et-al-2026-recommendations-in-extracorporeal-cardiopulmonary-resuscitation-post-resuscitation-care-via-an.pdf</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Recommendations in Extracorporeal Cardiopulmonary Resuscitation Post Resuscitation Care Via An International, Modified Delphi Approach</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mark Dennis et al.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Journal of the American Heart Association</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>10.1161/JAHA.125.047548</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:38:29</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>prabhakaran-et-al-2026-2026-guideline-for-the-early-management-of-patients-with-acute-ischemic-stroke-a-guideline-from.pdf</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026 Guideline for the Early Management of Patients With Acute Ischemic Stroke: A Guideline From the American Heart Association/American Stroke Association</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Shyam Prabhakaran et al.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Stroke</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>10.1161/STR.0000000000000513</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neurology</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:40:32</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>rccm.202507-1692st.pdf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Diagnosis and Management of Community-acquired Pneumonia: An Official American Thoracic Society Clinical Practice Guideline</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Barbara E. Jones et al.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>American Journal of Respiratory and Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>10.1164/rccm.202507-1692ST</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:41:40</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>s12028-023-01752-y (1).pdf</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Intracranial Pressure Monitoring and Management in Aneurysmal Subarachnoid Hemorrhage</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Alberto Addis et al.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Neurocritical Care</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>10.1007/s12028-023-01752-y</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neurology</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:42:53</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>surviving_sepsis_campaign__international.5 (1).pdf</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Surviving Sepsis Campaign: International Guidelines for Management of Sepsis and Septic Shock 2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Hallie C. Prescott et al.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>10.1097/CCM.0000000000007075</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sepsis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:44:49</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="44.6640625" customWidth="1" min="2" max="2"/>
@@ -5925,13 +5925,1183 @@
           <t>2026-06-30 14:08:25</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Left ventricular outflow tract obstruction in critically ill patients.pdf</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Left ventricular outflow tract obstruction in critically ill patients: from pathophysiology and diagnosis to the management with the “LVOTO” bundle</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Julia Trzebicka, Maciej Tysarowski, Filippo Sanfilippo, Filipe A Gonzalez, Michel Slama, Mateusz Zawadka</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Anaesthesia Critical Care &amp; Pain Medicine</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>10.1016/j.accpm.2026.101770</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:21:42</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>life-16-00913.pdf</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Optimizing Timing and Dose of Starting Norepinephrine and Vasopressin in Septic Shock</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Gaku Hiroto, Mitsuaki Nishikimi, Nobuaki Shime</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10.3390/life16060913</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:22:46</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>medicina-62-01070 (1).pdf</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>The Right Ventricle in Cardiac Critical Care: Pathophysiology, Evaluation and Management</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Aristi Boulmpou et al.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10.3390/medicina62061070</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:24:57</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>medicina-62-01070.pdf</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The Right Ventricle in Cardiac Critical Care: Pathophysiology, Evaluation and Management</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Aristi Boulmpou et al.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10.3390/medicina62061070</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:27:25</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PIIS0007091225009353.pdf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Optimising positive end-expiratory pressure in acute respiratory distress syndrome: a narrative review of approaches to titration</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Adriano Servetti et al.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>British Journal of Anaesthesia</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>10.1016/j.bja.2025.12.048</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:28:48</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PIIS0007091226002734.pdf</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Patient Blood Management: a systematic review of current international guidelines</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Daniel Dreher et al.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>British Journal of Anaesthesia</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10.1016/j.bja.2026.03.055</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hematology</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:29:29</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PIIS0007091226003296.pdf</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Agreement of minimally invasive pulse wave analysis with pulmonary artery and transpulmonary thermodilution cardiac output measurements in perioperative and intensive care medicine: a systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Flick M et al.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>British Journal of Anaesthesia</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>10.1016/j.bja.2026.04.045</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:30:19</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>s00134-026-08491-6.pdf</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Patient blood management in general intensive care patients</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Patrick Meybohm et al.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Intensive Care Medicine</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>10.1007/s00134-026-08491-6</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:31:23</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>s13054-026-06075-w.pdf</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Intrapulmonary penetration of ceftolozane/tazobactam and ceftazidime/avibactam administered by continuous infusion in critically ill patients with nosocomial pneumonia: a randomized pharmacokinetic trial</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Adela Benítez-Cano et al.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Critical Care</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>10.1186/s13054-026-06075-w</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:32:42</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>s13054-026-06075-w.pdf.xml.pdf</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Intrapulmonary penetration of ceftolozane/tazobactam and ceftazidime/avibactam administered by continuous infusion in critically ill patients with nosocomial pneumonia: a randomized pharmacokinetic trial</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Adela Benítez-Cano et al.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Critical Care</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>10.1186/s13054-026-06075-w</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:33:45</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>The effects of asymmetrical versus symmetrical high-flow nasal cannula on respiratory muscle activity in acute hypoxaemic respiratory failure and chro.pdf</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>The effects of asymmetrical versus symmetrical high-flow nasal cannula on respiratory muscle activity in acute hypoxaemic respiratory failure and chronic obstructive pulmonary disease: A randomised crossover study</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chakorn Lapanan et al.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>10.1080/25310429.2026.2694247</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:34:38</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>the_vicious_cycle__delirium,_sedation,_and_patient.7.pdf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>The vicious cycle: Delirium, sedation, and patient outcomes in critical care</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Shibu Sasidharan, Harpreet Dhillon</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Current Medicine Research and Practice</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>10.4103/cmrp.cmrp_42_25</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:35:52</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>adedinsewo-et-al-2026-heart-failure-occurring-in-the-perinatal-period-a-scientific-statement-from-the-american-heart.pdf</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Heart Failure Occurring in the Perinatal Period: A Scientific Statement From the American Heart Association</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>10.1161/CIR.0000000000001450</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:37:33</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>howard-quijano-et-al-2026-perioperative-anemia-and-patient-blood-management-in-cardiac-surgery-a-scientific-statement.pdf</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Perioperative Anemia and Patient Blood Management in Cardiac Surgery: A Scientific Statement From the American Heart Association</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>10.1161/CIR.0000000000001446</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:38:29</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ruel-et-al-2026-secondary-prevention-after-coronary-artery-bypass-graft-surgery-2026-update-a-scientific-statement-from.pdf</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Secondary Prevention After Coronary Artery Bypass Graft Surgery: 2026 Update: A Scientific Statement From the American Heart Association</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>10.1161/CIR.0000000000001434</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:40:21</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>s00330-026-12440-8.pdf</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ESR Essentials: trauma team and the role of Interventional Radiology — practice recommendations by the Cardiovascular and Interventional Radiological Society of Europe</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>10.1007/s00330-026-12440-8</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Trauma</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:40:58</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>s00508-026-02771-3.pdf</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Resuscitative thoracotomy in traumatic cardiac arrest: Multisociety consensus recommendations for settings with a low prevalence of penetrating injuries</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>10.1007/s00508-026-02771-3</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Trauma</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:42:25</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ti-39-16284.pdf</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Establishing standards for controlled donation after circulatory determination of death in adults: the Bucharest international European Society for Organ Transplantation consensus</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>10.3389/ti.2026.16284</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:44:41</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="44.6640625" customWidth="1" min="2" max="2"/>
@@ -7095,13 +7095,1113 @@
           <t>2026-06-30 16:44:41</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>efficacy_and_safety_of_systemic_prophylactic.861.pdf</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Efficacy and Safety of Systemic Prophylactic Antibacterials in Mechanically Ventilated Patients: Systematic Review and Meta-Analysis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Qiuying Yu et al.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Critical Care Medicine</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>10.1097/CCM.0000000000007183</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:06:01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Endovascular_Thrombectomy_in_Medium_and_Distal_Vessel_Occlusions.pdf</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Endovascular Thrombectomy in Medium and Distal Vessel Occlusions: A Focused Guideline From the Society of Vascular and Interventional Neurology Guidelines and Practice Standards Committee</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>10.1161/SVIN.125.002314</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Neurology</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:07:27</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>fcvm-13-1836476 (1).pdf</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Treatment of supraventricular arrhythmias in critical care patients with sepsis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Tencer T, Waldauf P, Balik M</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Frontiers in Cardiovascular Medicine</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>10.3389/fcvm.2026.1836476</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:09:22</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>fcvm-13-1836476.pdf</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Treatment of supraventricular arrhythmias in critical care patients with sepsis</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tencer T, Waldauf P, Balik M</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Frontiers in Cardiovascular Medicine</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>10.3389/fcvm.2026.1836476</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:10:37</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>jcm-15-04345.pdf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Lung Imaging in Acute Hypoxemic Respiratory Failure: From Physics to Bedside Applications</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Silvia Coppola et al.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Journal of Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>10.3390/jcm15114345</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:11:44</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Pathophysiology of Ketoacidosis.pdf</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Pathophysiology of Ketoacidosis: Core Curriculum 2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Biff F. Palmer and Deborah J. Clegg</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>American Journal of Kidney Diseases</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>10.1053/j.ajkd.2026.02.646</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Nephrology</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:13:24</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Renal_congestion_in_Critically_Ill_a_neglected_mechanism_of_AKI.pdf</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Renal congestion syndrome in critically ill patients: a neglected mechanism of acute kidney injury - A narrative review</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Arthur Orieux et al.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Annals of Intensive Care</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>10.1016/j.aicoj.2026.100083</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Nephrology</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:14:42</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>s13054-026-06123-5.pdf</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Current concepts on feeding the critically ill patient: a narrative review</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Michael Adolph et al.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Critical Care</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>10.1186/s13054-026-06123-5</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:16:29</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sickle cell emergencies.pdf</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Guidelines for the management of emergencies and critical illness in pediatric and adult patients with sickle cell disease</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>10.1186/s13613-025-01479-3</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hematology</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:18:28</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Systemic_corticosteroids_for_severe_community_acquired_pneumonia.pdf</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Systemic corticosteroids for severe community-acquired pneumonia: a narrative review of mechanisms and critical appraisal of recent trials in ICU</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Benjamin Eastwood et al.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>European Respiratory Review</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>10.1183/16000617.0259-2025</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:19:27</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Usual-care mobilisation of adult patients inthe intensive care unit.pdf</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Practical Guide: Usual-care mobilisation of adult patients in the intensive care unit</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Paton M, Hodgson CL</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Journal of Physiotherapy</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>10.1016/j.jphys.2026.06.004</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:21:22</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Eur Respir Rev-2022-Lamoth-220114.pdf</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Pulmonary aspergillosis: diagnosis and treatment</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Lamoth F, Calandra T</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>European Respiratory Review</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>10.1183/16000617.0114-2022</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Pulmonology</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:22:54</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ISCCM guidelines for CRE CRAB and CRPA.pdf</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Indian Society of Critical Care Medicine Guidelines on Evidence-based Recommendations for the Treatment of Carbapenem-resistant Enterobacterales, Carbapenem-resistant Acinetobacter baumannii, and Carbapenem-resistant Pseudomonas aeruginosa in Critically Ill Patients: A GRADE-guided Approach</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>10.5005/jp-journals-10071-25216</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:24:01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>MYC-68-e70132.pdf</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Management of Invasive Pulmonary Aspergillosis in Intensive Care Units: Guidelines From the Fungal Infection Network of Switzerland (FUNGINOS)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>10.1111/myc.70132</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:25:39</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>WHO guidelines on Central venous catheters.pdf</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Guidelines for the prevention of bloodstream infections and other infections associated with the use of intravascular catheters. Part 2: central venous catheters</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>978-92-4-012180-5</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:28:55</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>WHO guidelines on Peripheral Catheters.pdf</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Guidelines for the prevention of bloodstream infections and other infections associated with the use of intravascular catheters. Part I: peripheral catheters</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>978-92-4-009382-9</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:30:31</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>WHO practical manual on meningitis diagnosis.pdf</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>WHO practical manual on meningitis diagnosis, treatment and care</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Unknown Authors</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Unknown Journal</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>guideline</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:31:56</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RONAK\AI Projects\ACUMEN\ai-microlearning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D673DE-887D-4847-A008-1082C0150CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C635D71-4DAB-4CE2-9078-07EAD561C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="673">
   <si>
     <t>Serial Number</t>
   </si>
@@ -1745,9 +1745,6 @@
   </si>
   <si>
     <t>10.1161/CIR.0000000000001450</t>
-  </si>
-  <si>
-    <t>guideline</t>
   </si>
   <si>
     <t>2026-06-30 16:37:33</t>
@@ -6385,16 +6382,16 @@
         <v>150</v>
       </c>
       <c r="H99" t="s">
+        <v>74</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>53</v>
+      </c>
+      <c r="K99" t="s">
         <v>574</v>
-      </c>
-      <c r="I99" t="s">
-        <v>21</v>
-      </c>
-      <c r="J99" t="s">
-        <v>53</v>
-      </c>
-      <c r="K99" t="s">
-        <v>575</v>
       </c>
       <c r="M99" t="s">
         <v>24</v>
@@ -6408,10 +6405,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>575</v>
+      </c>
+      <c r="C100" t="s">
         <v>576</v>
-      </c>
-      <c r="C100" t="s">
-        <v>577</v>
       </c>
       <c r="D100" t="s">
         <v>571</v>
@@ -6420,13 +6417,13 @@
         <v>572</v>
       </c>
       <c r="F100" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G100" t="s">
         <v>474</v>
       </c>
       <c r="H100" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I100" t="s">
         <v>21</v>
@@ -6435,7 +6432,7 @@
         <v>53</v>
       </c>
       <c r="K100" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M100" t="s">
         <v>24</v>
@@ -6449,10 +6446,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>579</v>
+      </c>
+      <c r="C101" t="s">
         <v>580</v>
-      </c>
-      <c r="C101" t="s">
-        <v>581</v>
       </c>
       <c r="D101" t="s">
         <v>571</v>
@@ -6461,13 +6458,13 @@
         <v>572</v>
       </c>
       <c r="F101" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G101" t="s">
         <v>150</v>
       </c>
       <c r="H101" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I101" t="s">
         <v>21</v>
@@ -6476,7 +6473,7 @@
         <v>53</v>
       </c>
       <c r="K101" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M101" t="s">
         <v>24</v>
@@ -6490,10 +6487,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>583</v>
+      </c>
+      <c r="C102" t="s">
         <v>584</v>
-      </c>
-      <c r="C102" t="s">
-        <v>585</v>
       </c>
       <c r="D102" t="s">
         <v>571</v>
@@ -6502,13 +6499,13 @@
         <v>572</v>
       </c>
       <c r="F102" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G102" t="s">
         <v>66</v>
       </c>
       <c r="H102" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I102" t="s">
         <v>21</v>
@@ -6517,7 +6514,7 @@
         <v>53</v>
       </c>
       <c r="K102" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M102" t="s">
         <v>24</v>
@@ -6531,10 +6528,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>587</v>
+      </c>
+      <c r="C103" t="s">
         <v>588</v>
-      </c>
-      <c r="C103" t="s">
-        <v>589</v>
       </c>
       <c r="D103" t="s">
         <v>571</v>
@@ -6543,13 +6540,13 @@
         <v>572</v>
       </c>
       <c r="F103" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G103" t="s">
         <v>66</v>
       </c>
       <c r="H103" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I103" t="s">
         <v>21</v>
@@ -6558,7 +6555,7 @@
         <v>53</v>
       </c>
       <c r="K103" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M103" t="s">
         <v>24</v>
@@ -6572,10 +6569,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>591</v>
+      </c>
+      <c r="C104" t="s">
         <v>592</v>
-      </c>
-      <c r="C104" t="s">
-        <v>593</v>
       </c>
       <c r="D104" t="s">
         <v>571</v>
@@ -6584,13 +6581,13 @@
         <v>572</v>
       </c>
       <c r="F104" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G104" t="s">
         <v>237</v>
       </c>
       <c r="H104" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I104" t="s">
         <v>21</v>
@@ -6599,7 +6596,7 @@
         <v>53</v>
       </c>
       <c r="K104" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M104" t="s">
         <v>24</v>
@@ -6613,19 +6610,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>595</v>
+      </c>
+      <c r="C105" t="s">
         <v>596</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>597</v>
-      </c>
-      <c r="D105" t="s">
-        <v>598</v>
       </c>
       <c r="E105" t="s">
         <v>258</v>
       </c>
       <c r="F105" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G105" t="s">
         <v>19</v>
@@ -6640,7 +6637,7 @@
         <v>53</v>
       </c>
       <c r="K105" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="M105" t="s">
         <v>24</v>
@@ -6654,10 +6651,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>600</v>
+      </c>
+      <c r="C106" t="s">
         <v>601</v>
-      </c>
-      <c r="C106" t="s">
-        <v>602</v>
       </c>
       <c r="D106" t="s">
         <v>571</v>
@@ -6666,13 +6663,13 @@
         <v>572</v>
       </c>
       <c r="F106" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G106" t="s">
         <v>81</v>
       </c>
       <c r="H106" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I106" t="s">
         <v>21</v>
@@ -6681,7 +6678,7 @@
         <v>53</v>
       </c>
       <c r="K106" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="M106" t="s">
         <v>24</v>
@@ -6695,19 +6692,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>604</v>
+      </c>
+      <c r="C107" t="s">
         <v>605</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>606</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>607</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>608</v>
-      </c>
-      <c r="F107" t="s">
-        <v>609</v>
       </c>
       <c r="G107" t="s">
         <v>150</v>
@@ -6722,7 +6719,7 @@
         <v>53</v>
       </c>
       <c r="K107" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="M107" t="s">
         <v>24</v>
@@ -6736,19 +6733,19 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C108" t="s">
+        <v>605</v>
+      </c>
+      <c r="D108" t="s">
         <v>606</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>607</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>608</v>
-      </c>
-      <c r="F108" t="s">
-        <v>609</v>
       </c>
       <c r="G108" t="s">
         <v>150</v>
@@ -6763,7 +6760,7 @@
         <v>53</v>
       </c>
       <c r="K108" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="M108" t="s">
         <v>24</v>
@@ -6777,19 +6774,19 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>612</v>
+      </c>
+      <c r="C109" t="s">
         <v>613</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>614</v>
-      </c>
-      <c r="D109" t="s">
-        <v>615</v>
       </c>
       <c r="E109" t="s">
         <v>101</v>
       </c>
       <c r="F109" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G109" t="s">
         <v>19</v>
@@ -6804,7 +6801,7 @@
         <v>53</v>
       </c>
       <c r="K109" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M109" t="s">
         <v>24</v>
@@ -6818,19 +6815,19 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>617</v>
+      </c>
+      <c r="C110" t="s">
         <v>618</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>619</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>620</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>621</v>
-      </c>
-      <c r="F110" t="s">
-        <v>622</v>
       </c>
       <c r="G110" t="s">
         <v>30</v>
@@ -6845,7 +6842,7 @@
         <v>53</v>
       </c>
       <c r="K110" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M110" t="s">
         <v>24</v>
@@ -6859,19 +6856,19 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>623</v>
+      </c>
+      <c r="C111" t="s">
         <v>624</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>625</v>
-      </c>
-      <c r="D111" t="s">
-        <v>626</v>
       </c>
       <c r="E111" t="s">
         <v>44</v>
       </c>
       <c r="F111" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G111" t="s">
         <v>30</v>
@@ -6886,7 +6883,7 @@
         <v>53</v>
       </c>
       <c r="K111" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="M111" t="s">
         <v>24</v>
@@ -6900,19 +6897,19 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>628</v>
+      </c>
+      <c r="C112" t="s">
         <v>629</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>630</v>
-      </c>
-      <c r="D112" t="s">
-        <v>631</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
       </c>
       <c r="F112" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G112" t="s">
         <v>237</v>
@@ -6927,7 +6924,7 @@
         <v>53</v>
       </c>
       <c r="K112" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M112" t="s">
         <v>24</v>
@@ -6941,10 +6938,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
+        <v>633</v>
+      </c>
+      <c r="C113" t="s">
         <v>634</v>
-      </c>
-      <c r="C113" t="s">
-        <v>635</v>
       </c>
       <c r="D113" t="s">
         <v>571</v>
@@ -6953,13 +6950,13 @@
         <v>572</v>
       </c>
       <c r="F113" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G113" t="s">
         <v>391</v>
       </c>
       <c r="H113" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I113" t="s">
         <v>21</v>
@@ -6968,7 +6965,7 @@
         <v>53</v>
       </c>
       <c r="K113" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M113" t="s">
         <v>24</v>
@@ -6982,19 +6979,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
+        <v>637</v>
+      </c>
+      <c r="C114" t="s">
         <v>638</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>639</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>640</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>641</v>
-      </c>
-      <c r="F114" t="s">
-        <v>642</v>
       </c>
       <c r="G114" t="s">
         <v>19</v>
@@ -7009,7 +7006,7 @@
         <v>53</v>
       </c>
       <c r="K114" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M114" t="s">
         <v>24</v>
@@ -7023,19 +7020,19 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
+        <v>643</v>
+      </c>
+      <c r="C115" t="s">
         <v>644</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>645</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>646</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>647</v>
-      </c>
-      <c r="F115" t="s">
-        <v>648</v>
       </c>
       <c r="G115" t="s">
         <v>19</v>
@@ -7050,7 +7047,7 @@
         <v>53</v>
       </c>
       <c r="K115" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M115" t="s">
         <v>24</v>
@@ -7064,19 +7061,19 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>649</v>
+      </c>
+      <c r="C116" t="s">
         <v>650</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>651</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
+        <v>640</v>
+      </c>
+      <c r="F116" t="s">
         <v>652</v>
-      </c>
-      <c r="E116" t="s">
-        <v>641</v>
-      </c>
-      <c r="F116" t="s">
-        <v>653</v>
       </c>
       <c r="G116" t="s">
         <v>19</v>
@@ -7091,7 +7088,7 @@
         <v>53</v>
       </c>
       <c r="K116" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M116" t="s">
         <v>24</v>
@@ -7105,10 +7102,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>654</v>
+      </c>
+      <c r="C117" t="s">
         <v>655</v>
-      </c>
-      <c r="C117" t="s">
-        <v>656</v>
       </c>
       <c r="D117" t="s">
         <v>571</v>
@@ -7117,7 +7114,7 @@
         <v>572</v>
       </c>
       <c r="F117" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G117" t="s">
         <v>237</v>
@@ -7132,7 +7129,7 @@
         <v>53</v>
       </c>
       <c r="K117" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M117" t="s">
         <v>24</v>
@@ -7146,10 +7143,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>658</v>
+      </c>
+      <c r="C118" t="s">
         <v>659</v>
-      </c>
-      <c r="C118" t="s">
-        <v>660</v>
       </c>
       <c r="D118" t="s">
         <v>571</v>
@@ -7158,13 +7155,13 @@
         <v>572</v>
       </c>
       <c r="F118" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G118" t="s">
         <v>237</v>
       </c>
       <c r="H118" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I118" t="s">
         <v>21</v>
@@ -7173,7 +7170,7 @@
         <v>53</v>
       </c>
       <c r="K118" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="M118" t="s">
         <v>24</v>
@@ -7187,10 +7184,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>662</v>
+      </c>
+      <c r="C119" t="s">
         <v>663</v>
-      </c>
-      <c r="C119" t="s">
-        <v>664</v>
       </c>
       <c r="D119" t="s">
         <v>571</v>
@@ -7199,13 +7196,13 @@
         <v>572</v>
       </c>
       <c r="F119" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G119" t="s">
         <v>237</v>
       </c>
       <c r="H119" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I119" t="s">
         <v>21</v>
@@ -7214,7 +7211,7 @@
         <v>53</v>
       </c>
       <c r="K119" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="M119" t="s">
         <v>24</v>
@@ -7228,10 +7225,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
+        <v>666</v>
+      </c>
+      <c r="C120" t="s">
         <v>667</v>
-      </c>
-      <c r="C120" t="s">
-        <v>668</v>
       </c>
       <c r="D120" t="s">
         <v>571</v>
@@ -7240,13 +7237,13 @@
         <v>572</v>
       </c>
       <c r="F120" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G120" t="s">
         <v>237</v>
       </c>
       <c r="H120" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I120" t="s">
         <v>21</v>
@@ -7255,7 +7252,7 @@
         <v>53</v>
       </c>
       <c r="K120" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="M120" t="s">
         <v>24</v>
@@ -7269,10 +7266,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>670</v>
+      </c>
+      <c r="C121" t="s">
         <v>671</v>
-      </c>
-      <c r="C121" t="s">
-        <v>672</v>
       </c>
       <c r="D121" t="s">
         <v>571</v>
@@ -7284,7 +7281,7 @@
         <v>237</v>
       </c>
       <c r="H121" t="s">
-        <v>574</v>
+        <v>74</v>
       </c>
       <c r="I121" t="s">
         <v>21</v>
@@ -7293,7 +7290,7 @@
         <v>53</v>
       </c>
       <c r="K121" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M121" t="s">
         <v>24</v>

--- a/sent_summaries.xlsx
+++ b/sent_summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RONAK\AI Projects\ACUMEN\ai-microlearning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C635D71-4DAB-4CE2-9078-07EAD561C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA89587-6E0D-446C-A1C5-AEE555ED4833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="669">
   <si>
     <t>Serial Number</t>
   </si>
@@ -1997,18 +1997,6 @@
   </si>
   <si>
     <t>2026-07-01 10:24:01</t>
-  </si>
-  <si>
-    <t>MYC-68-e70132.pdf</t>
-  </si>
-  <si>
-    <t>Management of Invasive Pulmonary Aspergillosis in Intensive Care Units: Guidelines From the Fungal Infection Network of Switzerland (FUNGINOS)</t>
-  </si>
-  <si>
-    <t>10.1111/myc.70132</t>
-  </si>
-  <si>
-    <t>2026-07-01 10:25:39</t>
   </si>
   <si>
     <t>WHO guidelines on Central venous catheters.pdf</t>
@@ -2384,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.6640625" customWidth="1"/>
@@ -7140,7 +7128,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B118" t="s">
         <v>658</v>
@@ -7181,7 +7169,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B119" t="s">
         <v>662</v>
@@ -7222,7 +7210,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B120" t="s">
         <v>666</v>
@@ -7236,9 +7224,6 @@
       <c r="E120" t="s">
         <v>572</v>
       </c>
-      <c r="F120" t="s">
-        <v>668</v>
-      </c>
       <c r="G120" t="s">
         <v>237</v>
       </c>
@@ -7252,50 +7237,12 @@
         <v>53</v>
       </c>
       <c r="K120" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="M120" t="s">
         <v>24</v>
       </c>
       <c r="N120" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <v>120</v>
-      </c>
-      <c r="B121" t="s">
-        <v>670</v>
-      </c>
-      <c r="C121" t="s">
-        <v>671</v>
-      </c>
-      <c r="D121" t="s">
-        <v>571</v>
-      </c>
-      <c r="E121" t="s">
-        <v>572</v>
-      </c>
-      <c r="G121" t="s">
-        <v>237</v>
-      </c>
-      <c r="H121" t="s">
-        <v>74</v>
-      </c>
-      <c r="I121" t="s">
-        <v>21</v>
-      </c>
-      <c r="J121" t="s">
-        <v>53</v>
-      </c>
-      <c r="K121" t="s">
-        <v>672</v>
-      </c>
-      <c r="M121" t="s">
-        <v>24</v>
-      </c>
-      <c r="N121" t="s">
         <v>53</v>
       </c>
     </row>
